--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D3CD6F-00ED-4738-BB07-1CC8A4EFBCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64EC160-CC0D-4A17-BFEE-0B8B3E654CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
@@ -254,61 +254,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>面接希望者一覧</t>
-    <rPh sb="0" eb="5">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日時設定による対応結果（日時・担当者）の閲覧</t>
-    <rPh sb="0" eb="4">
-      <t>メンセツニチジ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>スケジュール（カレンダー）への反映</t>
-    <rPh sb="15" eb="17">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接決定時、担当者へのメール配信</t>
-    <rPh sb="0" eb="5">
-      <t>メンセツケッテイジ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ハイシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
@@ -447,6 +392,614 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者登録</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募情報（氏名・カナ・性別・生年月日・メールアドレス・電話番号・郵便番号・住所・最終学歴・希望勤務地）の入力</t>
+    <rPh sb="1" eb="3">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <rPh sb="28" eb="32">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>サイシュウガクレキ</t>
+    </rPh>
+    <rPh sb="46" eb="51">
+      <t>キボウキンムチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・上記情報のDBへの登録</t>
+    <rPh sb="1" eb="5">
+      <t>ジョウキジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者状況一覧</t>
+    <rPh sb="1" eb="6">
+      <t>オウボシャジョウキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を一覧表示（応募者ID・氏名・カナ・性別・メールアドレス・電話番号・応募日・面接予定日・選考状況・更新日時・担当者・合否・更新ボタン）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ゴウヒ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ゴウヒ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・更新ボタンより変更・登録が可能</t>
+    <rPh sb="1" eb="3">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用関連部署全ユーザー</t>
+    <rPh sb="0" eb="2">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>カンレンブショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日・担当者登録、面接希望者状況一覧閲覧、スケジュールカレンダー</t>
+    <rPh sb="0" eb="3">
+      <t>メンセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者検索</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■スケジュールカレンダー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・採用スケジュールカレンダーへ自動反映</t>
+    <rPh sb="1" eb="3">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ジドウハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>氏名</t>
+    <rPh sb="0" eb="2">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カナ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>性別</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>生年月日</t>
+    <rPh sb="0" eb="4">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>電話番号</t>
+    <rPh sb="0" eb="4">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>郵便番号</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>住所</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>最終学歴</t>
+    <rPh sb="0" eb="4">
+      <t>サイシュウガクレキ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>希望勤務地</t>
+    <rPh sb="0" eb="5">
+      <t>キボウキンムチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>文字列</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>数値</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>全角</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ラジオボタン</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+年：1946～2026　月：1～12　日：1～31</t>
+    <rPh sb="6" eb="7">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ハイフンなし（ハイフンなしと表示する）</t>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+「中学校卒業」「高等学校卒業」「専門学校卒業」
+「短期大学卒業」「四年制大学卒業」「大学院修了」
+「その他」</t>
+    <rPh sb="7" eb="10">
+      <t>チュウガッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="14" eb="20">
+      <t>コウトウガッコウソツギョウ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>センモンガッコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>タンキダイガク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="39" eb="44">
+      <t>ヨネンセイダイガク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="48" eb="53">
+      <t>ダイガクインシュウリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+「東京」「神奈川」「愛知」「大阪」「福岡」</t>
+    <rPh sb="7" eb="9">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カナガワ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アイチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オオサカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フクオカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>件数増えることでのスケジュール重複</t>
+    <rPh sb="0" eb="3">
+      <t>ケンスウフ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>要再度対応</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1" eb="5">
+      <t>サイドタイオウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールにて担当者へ通知</t>
+    <rPh sb="5" eb="8">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一覧表示の際のデータ過多</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>表示に時間がかかる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ステータスの選択を作り、表示件数を絞る</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ヒョウジケンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シボ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件</t>
+    <rPh sb="0" eb="3">
+      <t>ヒキノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク管理システム</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>多方面での業務・各業務の増加による仕事の遅れやそれらを管理できていないことによる漏れが発生しているため。</t>
+    <rPh sb="0" eb="3">
+      <t>タホウメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>これらの課題を解消するため、見える化されたタスク管理システムの構築が必要となった。</t>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>本システムの導入により、個人としての管理はもちろん上長からもそれらを見える化を実現し、フォローアップの体制を整える。
+また、各業務の優先順位を明確にして進められるようにする。</t>
+    <rPh sb="51" eb="53">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>トトノ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="66" eb="70">
+      <t>ユウセンジュンイ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスクの登録</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>優先度・期限・完了日の登録</t>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>自身のTOPページへ表示</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスクのリマインド機能</t>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -469,218 +1022,13 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>個々の情報として面接日等閲覧可</t>
+      <t>タスクは個々の管理</t>
     </r>
-    <rPh sb="2" eb="7">
-      <t>ココノジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ナド</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エツラン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>個々に対するアクションとなり、全体としての進捗が見えにくい</t>
-    </r>
-    <rPh sb="2" eb="4">
+    <rPh sb="6" eb="8">
       <t>ココ</t>
     </rPh>
-    <rPh sb="5" eb="6">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>シンチョク</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>面接日等設定連絡の遅れや、面接日が先</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>伸ばしになるケースも</t>
-    </r>
-    <rPh sb="2" eb="4">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>レンラク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>メンセツヒ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ノ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>面接設定までの時間の短縮</t>
-    </r>
-    <rPh sb="2" eb="6">
-      <t>メンセツセッテイ</t>
-    </rPh>
     <rPh sb="9" eb="11">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>タンシュク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者登録</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>選考状況の見える化</t>
-    <rPh sb="0" eb="4">
-      <t>センコウジョウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="128"/>
-      </rPr>
-      <t>面接未設定の人・選考状況をを一覧でわかりやすくし、全体で進捗把握の強化</t>
-    </r>
-    <rPh sb="1" eb="6">
-      <t>メンセツミセッテイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="29" eb="33">
-      <t>シンチョクハアク</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>キョウカ</t>
+      <t>カンリ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -703,600 +1051,179 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>問い合わせのあった応募者を一覧（次回面接設定日・選考状況）で閲覧できるため</t>
+      <t>上長の把握は個々への確認となる</t>
     </r>
-    <rPh sb="2" eb="3">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジカイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>セッテイビ</t>
-    </rPh>
-    <rPh sb="26" eb="30">
-      <t>センコウジョウキョウ</t>
+    <rPh sb="2" eb="4">
+      <t>ジョウチョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハアク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ココ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>上長（管理者権限）からの登録・閲覧可</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウチョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>エツランカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>業務遅延や漏れがある</t>
+    </r>
+    <rPh sb="1" eb="5">
+      <t>ギョウムチエン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タスクを個々での管理＋上長での管理</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>ココ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウチョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>優先順位・期限等を見える化することで業務の遅延を防止（これらは上長からの変更も可）</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジュンイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ボウシ</t>
     </rPh>
     <rPh sb="32" eb="34">
-      <t>エツラン</t>
+      <t>ジョウチョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>・応募情報（氏名・カナ・性別・生年月日・メールアドレス・電話番号・郵便番号・住所・最終学歴・希望勤務地）の入力</t>
-    <rPh sb="1" eb="3">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <rPh sb="28" eb="32">
-      <t>デンワバンゴウ</t>
-    </rPh>
-    <rPh sb="33" eb="37">
-      <t>ユウビンバンゴウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ジュウショ</t>
-    </rPh>
-    <rPh sb="41" eb="45">
-      <t>サイシュウガクレキ</t>
-    </rPh>
-    <rPh sb="46" eb="51">
-      <t>キボウキンムチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・上記情報のDBへの登録</t>
-    <rPh sb="1" eb="5">
-      <t>ジョウキジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者状況一覧</t>
-    <rPh sb="1" eb="6">
-      <t>オウボシャジョウキョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募者情報を一覧表示（応募者ID・氏名・カナ・性別・メールアドレス・電話番号・応募日・面接予定日・選考状況・更新日時・担当者・合否・更新ボタン）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>業務完了が早くなるかつ漏れをなくす</t>
+    </r>
+    <rPh sb="2" eb="4">
+      <t>ギョウム</t>
     </rPh>
     <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="60" eb="63">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ゴウヒ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ゴウヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・更新ボタンより変更・登録が可能</t>
-    <rPh sb="1" eb="3">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用関連部署全ユーザー</t>
-    <rPh sb="0" eb="2">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>カンレンブショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日・担当者登録、面接希望者状況一覧閲覧、スケジュールカレンダー</t>
-    <rPh sb="0" eb="3">
-      <t>メンセツビ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者検索</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■スケジュールカレンダー</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・採用スケジュールカレンダーへ自動反映</t>
-    <rPh sb="1" eb="3">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ジドウハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>氏名</t>
-    <rPh sb="0" eb="2">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>カナ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>性別</t>
-    <rPh sb="0" eb="2">
-      <t>セイベツ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>生年月日</t>
-    <rPh sb="0" eb="4">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>データ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>メールアドレス</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>電話番号</t>
-    <rPh sb="0" eb="4">
-      <t>デンワバンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>郵便番号</t>
-    <rPh sb="0" eb="4">
-      <t>ユウビンバンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>住所</t>
-    <rPh sb="0" eb="2">
-      <t>ジュウショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>最終学歴</t>
-    <rPh sb="0" eb="4">
-      <t>サイシュウガクレキ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>希望勤務地</t>
-    <rPh sb="0" eb="5">
-      <t>キボウキンムチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>文字列</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>数値</t>
-    <rPh sb="0" eb="2">
-      <t>スウチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>全角</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ラジオボタン</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-年：1946～2026　月：1～12　日：1～31</t>
-    <rPh sb="6" eb="7">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ハイフンなし（ハイフンなしと表示する）</t>
-    <rPh sb="14" eb="16">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-「中学校卒業」「高等学校卒業」「専門学校卒業」
-「短期大学卒業」「四年制大学卒業」「大学院修了」
-「その他」</t>
-    <rPh sb="7" eb="10">
-      <t>チュウガッコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="14" eb="20">
-      <t>コウトウガッコウソツギョウ</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>センモンガッコウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>タンキダイガク</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="39" eb="44">
-      <t>ヨネンセイダイガク</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="48" eb="53">
-      <t>ダイガクインシュウリョウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-「東京」「神奈川」「愛知」「大阪」「福岡」</t>
-    <rPh sb="7" eb="9">
-      <t>トウキョウ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>カナガワ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>アイチ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>オオサカ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>フクオカ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>渡辺のぞみ</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>件数増えることでのスケジュール重複</t>
-    <rPh sb="0" eb="3">
-      <t>ケンスウフ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>チョウフク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>要再度対応</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="1" eb="5">
-      <t>サイドタイオウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>メールにて担当者へ通知</t>
-    <rPh sb="5" eb="8">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ツウチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>一覧表示の際のデータ過多</t>
-    <rPh sb="0" eb="4">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>表示に時間がかかる</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ステータスの選択を作り、表示件数を絞る</t>
-    <rPh sb="6" eb="8">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>ヒョウジケンスウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>シボ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>非機能要件</t>
-    <rPh sb="0" eb="3">
-      <t>ヒキノウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスク管理システム</t>
-    <rPh sb="3" eb="5">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>多方面での業務・各業務の増加による仕事の遅れやそれらを管理できていないことによる漏れが発生しているため。</t>
-    <rPh sb="0" eb="3">
-      <t>タホウメン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シゴト</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ハヤ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
       <t>モ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ハッセイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>これらの課題を解消するため、見える化されたタスク管理システムの構築が必要となった。</t>
-    <rPh sb="14" eb="15">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>本システムの導入により、個人としての管理はもちろん上長からもそれらを見える化を実現し、フォローアップの体制を整える。また、各業務の優先順位を明確にして進められるようにする。</t>
-    <rPh sb="51" eb="53">
-      <t>タイセイ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>トトノ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="65" eb="69">
-      <t>ユウセンジュンイ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>メイカク</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>スス</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1308,7 +1235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1412,12 +1339,6 @@
       <sz val="10"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1789,7 +1710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2012,9 +1933,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2024,8 +1942,56 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2033,29 +1999,74 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2075,75 +2086,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2153,27 +2095,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2195,9 +2116,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2207,13 +2125,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2225,8 +2143,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2636,44 +2554,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="86"/>
-      <c r="B6" s="87"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="88" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="86"/>
+      <c r="A6" s="90"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="90"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="86"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="88" t="s">
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="86"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="90"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2735,16 +2653,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="80"/>
-      <c r="H11" s="83" t="s">
+      <c r="G11" s="95"/>
+      <c r="H11" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2757,16 +2675,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="79" t="s">
+      <c r="F12" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="80"/>
-      <c r="H12" s="81">
+      <c r="G12" s="95"/>
+      <c r="H12" s="98">
         <v>46273</v>
       </c>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2779,16 +2697,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="79" t="s">
+      <c r="F13" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="80"/>
-      <c r="H13" s="81">
+      <c r="G13" s="95"/>
+      <c r="H13" s="98">
         <v>46273</v>
       </c>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2801,14 +2719,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="79" t="s">
+      <c r="F14" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="80"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -2945,22 +2863,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2973,52 +2891,52 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="107" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="109"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="104"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="114"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="109"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="104"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="112"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="101"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="107"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="114"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="109"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3044,427 +2962,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="115" t="s">
+      <c r="B4" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="115" t="s">
+      <c r="C4" s="111"/>
+      <c r="D4" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="115" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="117"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="115" t="s">
+      <c r="G4" s="112"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="116"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="111"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="100"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="118"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="93"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="94"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="123"/>
+      <c r="R6" s="124"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="89"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="90"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="94"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="124"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="93"/>
-      <c r="P8" s="93"/>
-      <c r="Q8" s="93"/>
-      <c r="R8" s="94"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="122"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="123"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="123"/>
+      <c r="Q8" s="123"/>
+      <c r="R8" s="124"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="89"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="94"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
+      <c r="M9" s="123"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="123"/>
+      <c r="R9" s="124"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
-      <c r="P10" s="93"/>
-      <c r="Q10" s="93"/>
-      <c r="R10" s="94"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="122"/>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="123"/>
+      <c r="R10" s="124"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="89"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="93"/>
-      <c r="O11" s="93"/>
-      <c r="P11" s="93"/>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="94"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="123"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="124"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="89"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="89"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="94"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="120"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="123"/>
+      <c r="R12" s="124"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="89"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="89"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="94"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="123"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="124"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="93"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="93"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="93"/>
-      <c r="P14" s="93"/>
-      <c r="Q14" s="93"/>
-      <c r="R14" s="94"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="123"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="123"/>
+      <c r="R14" s="124"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="93"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="93"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="93"/>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="93"/>
-      <c r="R15" s="94"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="124"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="93"/>
-      <c r="K16" s="93"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="93"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="94"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="123"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="123"/>
+      <c r="P16" s="123"/>
+      <c r="Q16" s="123"/>
+      <c r="R16" s="124"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="89"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="93"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="93"/>
-      <c r="R17" s="94"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="123"/>
+      <c r="R17" s="124"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="89"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="93"/>
-      <c r="P18" s="93"/>
-      <c r="Q18" s="93"/>
-      <c r="R18" s="94"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="124"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="93"/>
-      <c r="R19" s="94"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="121"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="122"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="124"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="93"/>
-      <c r="O20" s="93"/>
-      <c r="P20" s="93"/>
-      <c r="Q20" s="93"/>
-      <c r="R20" s="94"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="122"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="124"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="94"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="123"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="124"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
-      <c r="P22" s="93"/>
-      <c r="Q22" s="93"/>
-      <c r="R22" s="94"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="122"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="123"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="123"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="124"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3608,6 +3526,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:O2"/>
     <mergeCell ref="Q1:R1"/>
@@ -3616,78 +3606,6 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:R22"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3700,23 +3618,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="101" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3727,19 +3645,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3772,14 +3690,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3787,14 +3705,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="118" t="s">
+      <c r="K4" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="120"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="127"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4332,28 +4250,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="122" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="126"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="87"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4363,27 +4281,29 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74"/>
+      <c r="O2" s="74">
+        <v>46274</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -4423,27 +4343,27 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="127" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="127"/>
+      <c r="B5" s="88" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -4497,38 +4417,38 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="145" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="145"/>
-      <c r="D9" s="145"/>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
-      <c r="H9" s="145"/>
-      <c r="I9" s="145"/>
-      <c r="J9" s="145"/>
-      <c r="K9" s="145"/>
-      <c r="L9" s="145"/>
-      <c r="M9" s="145"/>
-      <c r="N9" s="145"/>
+      <c r="B9" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="89"/>
+      <c r="N9" s="89"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="145"/>
-      <c r="K10" s="145"/>
-      <c r="L10" s="145"/>
-      <c r="M10" s="145"/>
-      <c r="N10" s="145"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="89"/>
+      <c r="M10" s="89"/>
+      <c r="N10" s="89"/>
       <c r="O10" s="36"/>
     </row>
     <row r="11" spans="1:15">
@@ -4569,115 +4489,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
+      <c r="K13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="78"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
+      <c r="B14" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="78"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="78"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="78"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
+      <c r="B15" s="78" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="121" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="121"/>
+      <c r="B16" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="121" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
+      <c r="B17" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="78"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="121"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
@@ -4718,7 +4638,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4751,7 +4671,7 @@
       <c r="N22" s="44"/>
       <c r="O22" s="44"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5">
+    <row r="23" spans="1:15" ht="18" customHeight="1">
       <c r="A23" s="45"/>
       <c r="B23" s="45"/>
       <c r="C23" s="45"/>
@@ -4790,7 +4710,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4809,7 +4729,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4828,7 +4748,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4882,7 +4802,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4901,7 +4821,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4920,7 +4840,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4983,28 +4903,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="122" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="126"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="87"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -5014,27 +4934,27 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="75">
+      <c r="O2" s="74">
         <v>46266</v>
       </c>
     </row>
@@ -5115,11 +5035,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="128" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C7" s="129"/>
       <c r="D7" s="54" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5140,7 +5060,7 @@
       </c>
       <c r="C8" s="129"/>
       <c r="D8" s="17" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5604,16 +5524,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="122" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="123"/>
+      <c r="D1" s="84"/>
       <c r="E1" s="72" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5624,7 +5544,7 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
@@ -5635,16 +5555,16 @@
       <c r="O1" s="134"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5652,8 +5572,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5734,12 +5654,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5747,7 +5667,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5757,12 +5677,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5770,7 +5690,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5780,12 +5700,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5793,7 +5713,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5803,12 +5723,12 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="69" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="55"/>
@@ -5816,7 +5736,7 @@
       <c r="I10" s="55"/>
       <c r="J10" s="56"/>
       <c r="K10" s="132" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="L10" s="133"/>
       <c r="M10" s="31"/>
@@ -5851,7 +5771,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="43" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -5870,7 +5790,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="7" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C14" s="58"/>
       <c r="D14" s="58"/>
@@ -5889,7 +5809,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
@@ -5925,7 +5845,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C17" s="58"/>
       <c r="D17" s="58"/>
@@ -5944,7 +5864,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="58" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
@@ -5980,7 +5900,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="7" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -5999,7 +5919,7 @@
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="45"/>
       <c r="B21" s="58" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="45"/>
@@ -6018,7 +5938,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6054,7 +5974,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="43" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
@@ -6073,7 +5993,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -6229,23 +6149,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="122" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="126"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="87"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6260,17 +6180,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6768,28 +6688,28 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="122" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="126"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="87"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6799,17 +6719,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6883,11 +6803,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6899,7 +6819,7 @@
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6910,7 +6830,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
@@ -6926,7 +6846,7 @@
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6937,11 +6857,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6953,7 +6873,7 @@
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6964,11 +6884,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6979,23 +6899,23 @@
         <v>58</v>
       </c>
       <c r="I9" s="57"/>
-      <c r="J9" s="136" t="s">
-        <v>122</v>
-      </c>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="138"/>
+      <c r="J9" s="135" t="s">
+        <v>111</v>
+      </c>
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="137"/>
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="69" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="17" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E10" s="57"/>
       <c r="F10" s="17">
@@ -7016,11 +6936,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="17" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="17" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="17">
@@ -7032,7 +6952,7 @@
       </c>
       <c r="I11" s="57"/>
       <c r="J11" s="17" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -7043,11 +6963,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="17" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="17" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="17">
@@ -7059,7 +6979,7 @@
       </c>
       <c r="I12" s="57"/>
       <c r="J12" s="17" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7070,11 +6990,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="76"/>
+        <v>104</v>
+      </c>
+      <c r="C13" s="75"/>
       <c r="D13" s="17" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="17">
@@ -7094,12 +7014,12 @@
     </row>
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="76"/>
+      <c r="B14" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="75"/>
       <c r="D14" s="17" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="17">
@@ -7110,23 +7030,23 @@
         <v>58</v>
       </c>
       <c r="I14" s="57"/>
-      <c r="J14" s="139" t="s">
-        <v>124</v>
-      </c>
-      <c r="K14" s="140"/>
-      <c r="L14" s="140"/>
-      <c r="M14" s="141"/>
+      <c r="J14" s="138" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="140"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="76"/>
+      <c r="B15" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="75"/>
       <c r="D15" s="17" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="17">
@@ -7137,12 +7057,12 @@
         <v>58</v>
       </c>
       <c r="I15" s="57"/>
-      <c r="J15" s="142" t="s">
-        <v>125</v>
-      </c>
-      <c r="K15" s="143"/>
-      <c r="L15" s="143"/>
-      <c r="M15" s="144"/>
+      <c r="J15" s="141" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="143"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
@@ -7491,28 +7411,28 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="122" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="124" t="s">
+      <c r="D1" s="84"/>
+      <c r="E1" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="126"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="87"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7522,17 +7442,17 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="122"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="126"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="87"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7607,26 +7527,26 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="17" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
       <c r="P6" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -7635,21 +7555,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
-      <c r="M7" s="78" t="s">
-        <v>132</v>
+      <c r="M7" s="77" t="s">
+        <v>121</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64EC160-CC0D-4A17-BFEE-0B8B3E654CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2770728E-23E6-4623-9ECB-F7BBBEF119A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="139">
   <si>
     <t>要件定義</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>利用者区分</t>
-  </si>
-  <si>
-    <t>役割</t>
   </si>
   <si>
     <t>管理者</t>
@@ -268,13 +265,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>採用応募</t>
-    <rPh sb="0" eb="4">
-      <t>サイヨウオウボ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>応募者登録</t>
     <rPh sb="0" eb="5">
       <t>オウボシャトウロク</t>
@@ -589,31 +579,6 @@
     </rPh>
     <rPh sb="2" eb="6">
       <t>カンレンブショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日・担当者登録、面接希望者状況一覧閲覧、スケジュールカレンダー</t>
-    <rPh sb="0" eb="3">
-      <t>メンセツビ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>エツラン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1224,6 +1189,58 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <rPh sb="0" eb="2">
+      <t>イッパン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>役割・権限</t>
+    <rPh sb="3" eb="5">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク登録・更新</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>社員登録、タスク登録・更新（一般社員分も可）、社員のタスク閲覧</t>
+    <rPh sb="0" eb="4">
+      <t>シャイントウロク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>イッパンシャイン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>エツラン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1710,7 +1727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2145,6 +2162,9 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2558,7 +2578,7 @@
       <c r="B6" s="91"/>
       <c r="C6" s="92"/>
       <c r="D6" s="93" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E6" s="93"/>
       <c r="F6" s="93"/>
@@ -2658,7 +2678,7 @@
       </c>
       <c r="G11" s="95"/>
       <c r="H11" s="96" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I11" s="97"/>
       <c r="J11" s="97"/>
@@ -4271,7 +4291,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4296,7 +4316,7 @@
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
@@ -4344,7 +4364,7 @@
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="88" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C5" s="88"/>
       <c r="D5" s="88"/>
@@ -4363,7 +4383,7 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -4418,7 +4438,7 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="89" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C9" s="89"/>
       <c r="D9" s="89"/>
@@ -4509,7 +4529,7 @@
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="78" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C14" s="78"/>
       <c r="D14" s="78"/>
@@ -4528,7 +4548,7 @@
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="78" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C15" s="78"/>
       <c r="D15" s="78"/>
@@ -4547,7 +4567,7 @@
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
       <c r="B16" s="78" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="78"/>
@@ -4566,7 +4586,7 @@
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
       <c r="B17" s="78" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C17" s="78"/>
       <c r="D17" s="78"/>
@@ -4638,7 +4658,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4710,7 +4730,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4729,7 +4749,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4748,7 +4768,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4802,7 +4822,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4821,7 +4841,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4840,7 +4860,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4924,13 +4944,13 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="40">
-        <v>46260</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
@@ -4948,15 +4968,11 @@
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="26" t="s">
-        <v>71</v>
-      </c>
+      <c r="M2" s="26"/>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74">
-        <v>46266</v>
-      </c>
+      <c r="O2" s="74"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5017,8 +5033,8 @@
         <v>42</v>
       </c>
       <c r="C6" s="131"/>
-      <c r="D6" s="50" t="s">
-        <v>43</v>
+      <c r="D6" s="145" t="s">
+        <v>136</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -5035,11 +5051,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="128" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="C7" s="129"/>
-      <c r="D7" s="54" t="s">
-        <v>73</v>
+      <c r="D7" s="17" t="s">
+        <v>137</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5056,11 +5072,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="128" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="129"/>
       <c r="D8" s="17" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5533,7 +5549,7 @@
       </c>
       <c r="D1" s="84"/>
       <c r="E1" s="72" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5544,7 +5560,7 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
@@ -5595,7 +5611,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5631,12 +5647,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -5644,7 +5660,7 @@
       <c r="I6" s="52"/>
       <c r="J6" s="67"/>
       <c r="K6" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L6" s="56"/>
       <c r="M6" s="71"/>
@@ -5654,12 +5670,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5667,7 +5683,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5677,12 +5693,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5690,7 +5706,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5700,12 +5716,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5713,7 +5729,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5723,12 +5739,12 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="69" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="55"/>
@@ -5736,7 +5752,7 @@
       <c r="I10" s="55"/>
       <c r="J10" s="56"/>
       <c r="K10" s="132" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L10" s="133"/>
       <c r="M10" s="31"/>
@@ -5763,7 +5779,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -5771,7 +5787,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -5790,7 +5806,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" s="58"/>
       <c r="D14" s="58"/>
@@ -5809,7 +5825,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
@@ -5845,7 +5861,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C17" s="58"/>
       <c r="D17" s="58"/>
@@ -5864,7 +5880,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
@@ -5900,7 +5916,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -5919,7 +5935,7 @@
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="45"/>
       <c r="B21" s="58" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="45"/>
@@ -5938,7 +5954,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -5974,7 +5990,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="43" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
@@ -5993,7 +6009,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="58" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -6158,7 +6174,7 @@
       </c>
       <c r="D1" s="84"/>
       <c r="E1" s="85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F1" s="86"/>
       <c r="G1" s="86"/>
@@ -6220,7 +6236,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6239,7 +6255,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -6275,7 +6291,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -6294,7 +6310,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -6313,7 +6329,7 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -6693,11 +6709,11 @@
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D1" s="84"/>
       <c r="E1" s="85" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" s="86"/>
       <c r="G1" s="86"/>
@@ -6709,7 +6725,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6776,23 +6792,23 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="62"/>
       <c r="D5" s="61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I5" s="62"/>
       <c r="J5" s="61" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K5" s="55"/>
       <c r="L5" s="63"/>
@@ -6803,11 +6819,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6815,11 +6831,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6830,11 +6846,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="57"/>
       <c r="F7" s="54">
@@ -6842,11 +6858,11 @@
       </c>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6857,11 +6873,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6869,11 +6885,11 @@
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6884,11 +6900,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6896,11 +6912,11 @@
       </c>
       <c r="G9" s="57"/>
       <c r="H9" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="57"/>
       <c r="J9" s="135" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K9" s="136"/>
       <c r="L9" s="136"/>
@@ -6911,11 +6927,11 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="69" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E10" s="57"/>
       <c r="F10" s="17">
@@ -6923,7 +6939,7 @@
       </c>
       <c r="G10" s="57"/>
       <c r="H10" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="17"/>
@@ -6936,11 +6952,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="17">
@@ -6948,11 +6964,11 @@
       </c>
       <c r="G11" s="57"/>
       <c r="H11" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" s="57"/>
       <c r="J11" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -6963,11 +6979,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="17">
@@ -6975,11 +6991,11 @@
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I12" s="57"/>
       <c r="J12" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -6990,11 +7006,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="54" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="17">
@@ -7002,7 +7018,7 @@
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I13" s="57"/>
       <c r="J13" s="17"/>
@@ -7015,11 +7031,11 @@
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="76" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C14" s="75"/>
       <c r="D14" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="17">
@@ -7027,11 +7043,11 @@
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I14" s="57"/>
       <c r="J14" s="138" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K14" s="139"/>
       <c r="L14" s="139"/>
@@ -7042,11 +7058,11 @@
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="76" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C15" s="75"/>
       <c r="D15" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="17">
@@ -7054,11 +7070,11 @@
       </c>
       <c r="G15" s="57"/>
       <c r="H15" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I15" s="57"/>
       <c r="J15" s="141" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K15" s="142"/>
       <c r="L15" s="142"/>
@@ -7416,11 +7432,11 @@
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" s="84"/>
       <c r="E1" s="85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F1" s="86"/>
       <c r="G1" s="86"/>
@@ -7432,7 +7448,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7502,21 +7518,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="66"/>
       <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="66"/>
       <c r="J5" s="52"/>
       <c r="K5" s="52"/>
       <c r="L5" s="67"/>
       <c r="M5" s="61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
@@ -7527,26 +7543,26 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
       <c r="P6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -7555,21 +7571,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="77" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2770728E-23E6-4623-9ECB-F7BBBEF119A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE98E6-57EC-4AC6-8957-186DFFFCC1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="143">
   <si>
     <t>要件定義</t>
   </si>
@@ -258,172 +258,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>応募者</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者登録</t>
-    <rPh sb="0" eb="5">
-      <t>オウボシャトウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者が応募情報を登録</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="8">
-      <t>オウボジョウホウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者状況一覧</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者検索</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者の情報が一覧にて見える・更新ボタンにて面接決定日時の登録</t>
-    <rPh sb="0" eb="3">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ケッテイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>機能要件</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>応募者の検索ができる（入力時に使用）</t>
-    <rPh sb="0" eb="2">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ニュウリョクジ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用管理者</t>
-    <rPh sb="0" eb="2">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>カンリシャ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>スケジュール（カレンダー）</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>登録された面接日時をスケジュールカレンダーに反映</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>メンセツニチジ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者登録</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募情報（氏名・カナ・性別・生年月日・メールアドレス・電話番号・郵便番号・住所・最終学歴・希望勤務地）の入力</t>
-    <rPh sb="1" eb="3">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <rPh sb="28" eb="32">
-      <t>デンワバンゴウ</t>
-    </rPh>
-    <rPh sb="33" eb="37">
-      <t>ユウビンバンゴウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ジュウショ</t>
-    </rPh>
-    <rPh sb="41" eb="45">
-      <t>サイシュウガクレキ</t>
-    </rPh>
-    <rPh sb="46" eb="51">
-      <t>キボウキンムチ</t>
-    </rPh>
     <phoneticPr fontId="13"/>
   </si>
   <si>
@@ -437,126 +272,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>■応募者状況一覧</t>
-    <rPh sb="1" eb="6">
-      <t>オウボシャジョウキョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募者情報を一覧表示（応募者ID・氏名・カナ・性別・メールアドレス・電話番号・応募日・面接予定日・選考状況・更新日時・担当者・合否・更新ボタン）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="60" eb="63">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ゴウヒ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ゴウヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>・更新ボタンより変更・登録が可能</t>
     <rPh sb="1" eb="3">
       <t>コウシン</t>
@@ -569,40 +284,6 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用関連部署全ユーザー</t>
-    <rPh sb="0" eb="2">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>カンレンブショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者検索</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■スケジュールカレンダー</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・採用スケジュールカレンダーへ自動反映</t>
-    <rPh sb="1" eb="3">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ジドウハンエイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1244,6 +925,263 @@
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
+  <si>
+    <t>社員登録</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク登録</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク更新</t>
+    <rPh sb="3" eb="5">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2026/9/8.9</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>社員情報の登録</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一般社員・管理者</t>
+    <rPh sb="0" eb="2">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>管理者</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■社員登録</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■タスク登録</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■タスク更新</t>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■タスクの閲覧</t>
+    <rPh sb="5" eb="7">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■タスクのTOPページ表示</t>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・タスクの状況（期限、優先度、完了日）を更新</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>カンリョウビ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスクの状況を更新</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・一般社員は自身のタスクのみ閲覧可能
+</t>
+    <rPh sb="1" eb="3">
+      <t>イッパン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・管理者（上長）は全社員のタスクが閲覧可能</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスクの検索・閲覧</t>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>TOPページへのタスク表示</t>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>自身のタスクの中で、</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="double"/>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>当日・翌日が期限のものを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TOPページへ表示</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・自身のタスクの中で、当日・翌日が期限のものをTOPページへ表示</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・社員情報（氏名・カナ・性別・メールアドレス・部署）の入力</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>※社員ID・登録日時・更新日時・削除フラグはDB登録時に自動反映</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>トウロクジ</t>
+    </rPh>
+    <rPh sb="28" eb="32">
+      <t>ジドウハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・タスク情報（</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
 </sst>
 </file>
 
@@ -1252,7 +1190,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1365,6 +1303,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="double"/>
+      <sz val="10"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1727,7 +1673,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2124,12 +2070,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2164,6 +2104,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2578,7 +2521,7 @@
       <c r="B6" s="91"/>
       <c r="C6" s="92"/>
       <c r="D6" s="93" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="E6" s="93"/>
       <c r="F6" s="93"/>
@@ -4296,8 +4239,8 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
-        <v>46273</v>
+      <c r="O1" s="40" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
@@ -4315,15 +4258,11 @@
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="26" t="s">
-        <v>70</v>
-      </c>
+      <c r="M2" s="26"/>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74">
-        <v>46274</v>
-      </c>
+      <c r="O2" s="74"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -4364,7 +4303,7 @@
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="88" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C5" s="88"/>
       <c r="D5" s="88"/>
@@ -4383,7 +4322,7 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -4438,7 +4377,7 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="89" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C9" s="89"/>
       <c r="D9" s="89"/>
@@ -4529,7 +4468,7 @@
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="78" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="C14" s="78"/>
       <c r="D14" s="78"/>
@@ -4548,7 +4487,7 @@
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="78" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C15" s="78"/>
       <c r="D15" s="78"/>
@@ -4567,7 +4506,7 @@
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
       <c r="B16" s="78" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="C16" s="78"/>
       <c r="D16" s="78"/>
@@ -4586,7 +4525,7 @@
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
       <c r="B17" s="78" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C17" s="78"/>
       <c r="D17" s="78"/>
@@ -4658,7 +4597,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4730,7 +4669,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4749,7 +4688,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4768,7 +4707,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4822,7 +4761,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4841,7 +4780,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4860,7 +4799,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5033,8 +4972,8 @@
         <v>42</v>
       </c>
       <c r="C6" s="131"/>
-      <c r="D6" s="145" t="s">
-        <v>136</v>
+      <c r="D6" s="143" t="s">
+        <v>117</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -5051,11 +4990,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="128" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C7" s="129"/>
       <c r="D7" s="17" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5076,7 +5015,7 @@
       </c>
       <c r="C8" s="129"/>
       <c r="D8" s="17" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5533,7 +5472,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8D2F9E-DCA9-4610-96AE-118D7871E7D7}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="10" max="10" width="10.4140625" customWidth="1"/>
@@ -5549,7 +5488,7 @@
       </c>
       <c r="D1" s="84"/>
       <c r="E1" s="72" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5565,10 +5504,10 @@
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="134">
-        <v>46260</v>
-      </c>
-      <c r="O1" s="134"/>
+      <c r="N1" s="132">
+        <v>46274</v>
+      </c>
+      <c r="O1" s="132"/>
     </row>
     <row r="2" spans="1:15" ht="20">
       <c r="A2" s="81"/>
@@ -5588,8 +5527,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="142"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5670,12 +5609,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5683,7 +5622,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5693,12 +5632,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5706,7 +5645,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5716,12 +5655,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5729,7 +5668,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5739,82 +5678,86 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="132" t="s">
-        <v>89</v>
-      </c>
-      <c r="L10" s="133"/>
+      <c r="E10" s="133" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="L10" s="56"/>
       <c r="M10" s="31"/>
       <c r="N10" s="36"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="B11" s="133" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="134"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="144" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="70" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" s="56"/>
+      <c r="M11" s="31"/>
       <c r="N11" s="36"/>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
-      <c r="B12" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
-      <c r="B13" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="7"/>
+      <c r="B13" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
-      <c r="B14" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
+      <c r="B14" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="J14" s="43"/>
       <c r="K14" s="43"/>
       <c r="L14" s="43"/>
@@ -5825,14 +5768,16 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
       <c r="E15" s="58"/>
       <c r="F15" s="58"/>
       <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
+      <c r="H15" s="58" t="s">
+        <v>141</v>
+      </c>
       <c r="I15" s="58"/>
       <c r="J15" s="43"/>
       <c r="K15" s="43"/>
@@ -5843,7 +5788,9 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="36"/>
-      <c r="B16" s="7"/>
+      <c r="B16" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="C16" s="58"/>
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
@@ -5860,9 +5807,7 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
-      <c r="B17" s="7" t="s">
-        <v>90</v>
-      </c>
+      <c r="B17" s="7"/>
       <c r="C17" s="58"/>
       <c r="D17" s="58"/>
       <c r="E17" s="58"/>
@@ -5879,16 +5824,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
+      <c r="B18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
       <c r="J18" s="43"/>
       <c r="K18" s="43"/>
       <c r="L18" s="43"/>
@@ -5898,7 +5843,9 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
-      <c r="B19" s="31"/>
+      <c r="B19" s="58" t="s">
+        <v>142</v>
+      </c>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
       <c r="E19" s="43"/>
@@ -5915,9 +5862,7 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
-      <c r="B20" s="7" t="s">
-        <v>85</v>
-      </c>
+      <c r="B20" s="31"/>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
@@ -5932,66 +5877,66 @@
       <c r="N20" s="43"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15" ht="18" customHeight="1">
-      <c r="A21" s="45"/>
-      <c r="B21" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
+    <row r="21" spans="1:15">
+      <c r="A21" s="36"/>
+      <c r="B21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
+      <c r="A22" s="45"/>
+      <c r="B22" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" ht="18" customHeight="1">
       <c r="A23" s="8"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
+      <c r="B23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
       <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="43" t="s">
-        <v>91</v>
-      </c>
+      <c r="B24" s="58"/>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
@@ -6008,8 +5953,8 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58" t="s">
-        <v>92</v>
+      <c r="B25" s="43" t="s">
+        <v>130</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -6027,7 +5972,9 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
+      <c r="B26" s="58" t="s">
+        <v>134</v>
+      </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
       <c r="E26" s="47"/>
@@ -6044,7 +5991,9 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="47"/>
+      <c r="B27" s="58" t="s">
+        <v>135</v>
+      </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
       <c r="E27" s="47"/>
@@ -6061,41 +6010,45 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
       <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
+      <c r="B29" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="47"/>
       <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -6144,9 +6097,44 @@
       <c r="N32" s="8"/>
       <c r="O32" s="7"/>
     </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="K10:L10"/>
+  <mergeCells count="8">
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="N1:O1"/>
@@ -6725,7 +6713,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6819,11 +6807,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6835,7 +6823,7 @@
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6846,7 +6834,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
@@ -6862,7 +6850,7 @@
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6873,11 +6861,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6889,7 +6877,7 @@
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6900,11 +6888,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6915,23 +6903,23 @@
         <v>57</v>
       </c>
       <c r="I9" s="57"/>
-      <c r="J9" s="135" t="s">
-        <v>108</v>
-      </c>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="137"/>
+      <c r="J9" s="133" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="135"/>
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="69" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="17" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E10" s="57"/>
       <c r="F10" s="17">
@@ -6952,11 +6940,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="17" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="17" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="17">
@@ -6968,7 +6956,7 @@
       </c>
       <c r="I11" s="57"/>
       <c r="J11" s="17" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -6979,11 +6967,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="17" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="17" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="17">
@@ -6995,7 +6983,7 @@
       </c>
       <c r="I12" s="57"/>
       <c r="J12" s="17" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7006,11 +6994,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="54" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="17">
@@ -7031,11 +7019,11 @@
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="76" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C14" s="75"/>
       <c r="D14" s="17" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="17">
@@ -7046,23 +7034,23 @@
         <v>57</v>
       </c>
       <c r="I14" s="57"/>
-      <c r="J14" s="138" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139"/>
-      <c r="M14" s="140"/>
+      <c r="J14" s="136" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="137"/>
+      <c r="L14" s="137"/>
+      <c r="M14" s="138"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="76" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C15" s="75"/>
       <c r="D15" s="17" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="17">
@@ -7073,12 +7061,12 @@
         <v>57</v>
       </c>
       <c r="I15" s="57"/>
-      <c r="J15" s="141" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" s="142"/>
-      <c r="L15" s="142"/>
-      <c r="M15" s="143"/>
+      <c r="J15" s="139" t="s">
+        <v>92</v>
+      </c>
+      <c r="K15" s="140"/>
+      <c r="L15" s="140"/>
+      <c r="M15" s="141"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
@@ -7448,7 +7436,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7543,26 +7531,26 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="17" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
       <c r="P6" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -7571,21 +7559,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="77" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFE98E6-57EC-4AC6-8957-186DFFFCC1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5A4285-6BAC-4F9F-956A-FD92F0712E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>業務要件</t>
   </si>
   <si>
-    <t>山田太郎</t>
-  </si>
-  <si>
     <t>1-1. システム化の背景</t>
   </si>
   <si>
@@ -173,16 +170,7 @@
     <t>4-1. 性能要件</t>
   </si>
   <si>
-    <t>・  1,000件の見積データに対し検索応答時間 1 秒以内</t>
-  </si>
-  <si>
     <t>4-2. セキュリティ要件</t>
-  </si>
-  <si>
-    <t>・  権限管理の実装</t>
-  </si>
-  <si>
-    <t>・  通信経路の HTTPS 暗号化</t>
   </si>
   <si>
     <t>データ項目定義</t>
@@ -1011,35 +999,9 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>■タスクの閲覧</t>
-    <rPh sb="5" eb="7">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>■タスクのTOPページ表示</t>
     <rPh sb="11" eb="13">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・タスクの状況（期限、優先度、完了日）を更新</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ユウセンド</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>カンリョウビ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1176,10 +1138,117 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>・タスク情報（</t>
+    <t>※登録者（社員ID）・登録日時・更新日時はDB登録時に自動反映</t>
+  </si>
+  <si>
+    <t>■タスクの検索・閲覧</t>
+    <rPh sb="5" eb="7">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・タスク情報（タスク名・タスク詳細・優先度（★、★★、★★★）・期限・ステータス（未着手、対応中、確認中、完了、保留）を登録　</t>
     <rPh sb="4" eb="6">
       <t>ジョウホウ</t>
     </rPh>
+    <rPh sb="10" eb="11">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>ミチャクシュ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>タイオウチュウ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ホリュウ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・タスクの状況（期限・優先度・ステータス・完了日）を更新</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>カンリョウビ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・タスクの検索（名前・タスク名・優先度・期限（当日、翌日、今週中）、ステータス）できるように</t>
+    <rPh sb="5" eb="7">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>コンシュウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>※管理者での検索画面のみ「名前」の入力欄を作成するか。</t>
+    <rPh sb="1" eb="4">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ケンサクガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ニュウリョクラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2026/9/9.10</t>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -1673,7 +1742,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1908,156 +1977,174 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2070,18 +2157,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2099,15 +2174,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2517,44 +2583,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="90"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="91"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="90"/>
+      <c r="A6" s="99"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="101"/>
+      <c r="J6" s="101"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="99"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="90"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="93" t="s">
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="90"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="101"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="100"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="99"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2616,12 +2682,12 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="94" t="s">
+      <c r="F11" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="95"/>
+      <c r="G11" s="93"/>
       <c r="H11" s="96" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I11" s="97"/>
       <c r="J11" s="97"/>
@@ -2638,16 +2704,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="94" t="s">
+      <c r="F12" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="95"/>
-      <c r="H12" s="98">
+      <c r="G12" s="93"/>
+      <c r="H12" s="94">
         <v>46273</v>
       </c>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="95"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2660,16 +2726,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="94" t="s">
+      <c r="F13" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="95"/>
-      <c r="H13" s="98">
+      <c r="G13" s="93"/>
+      <c r="H13" s="94">
         <v>46273</v>
       </c>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2682,10 +2748,10 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="94" t="s">
+      <c r="F14" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="95"/>
+      <c r="G14" s="93"/>
       <c r="H14" s="96"/>
       <c r="I14" s="97"/>
       <c r="J14" s="97"/>
@@ -2826,22 +2892,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2854,52 +2920,52 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="102" t="s">
+      <c r="B1" s="114"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="104"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="118"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="123"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="81"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="107"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="121"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="109"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="123"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -2925,427 +2991,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="110" t="s">
+      <c r="C4" s="125"/>
+      <c r="D4" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="111"/>
-      <c r="F4" s="110" t="s">
+      <c r="E4" s="125"/>
+      <c r="F4" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="112"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="110" t="s">
+      <c r="G4" s="126"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="111"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="126"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="125"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="118"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
+      <c r="N5" s="112"/>
+      <c r="O5" s="112"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="113"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="120"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="123"/>
-      <c r="M6" s="123"/>
-      <c r="N6" s="123"/>
-      <c r="O6" s="123"/>
-      <c r="P6" s="123"/>
-      <c r="Q6" s="123"/>
-      <c r="R6" s="124"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="107"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="119"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="119"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="119"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="124"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="107"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="124"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="106"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="106"/>
+      <c r="O8" s="106"/>
+      <c r="P8" s="106"/>
+      <c r="Q8" s="106"/>
+      <c r="R8" s="107"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="122"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="123"/>
-      <c r="L9" s="123"/>
-      <c r="M9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="124"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="106"/>
+      <c r="K9" s="106"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="106"/>
+      <c r="O9" s="106"/>
+      <c r="P9" s="106"/>
+      <c r="Q9" s="106"/>
+      <c r="R9" s="107"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="122"/>
-      <c r="J10" s="123"/>
-      <c r="K10" s="123"/>
-      <c r="L10" s="123"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="R10" s="124"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="106"/>
+      <c r="R10" s="107"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="124"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="106"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="106"/>
+      <c r="R11" s="107"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
-      <c r="M12" s="123"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="123"/>
-      <c r="R12" s="124"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="107"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="119"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="124"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="106"/>
+      <c r="R13" s="107"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="119"/>
-      <c r="C14" s="120"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="123"/>
-      <c r="M14" s="123"/>
-      <c r="N14" s="123"/>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="124"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="106"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="106"/>
+      <c r="R14" s="107"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="123"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="123"/>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="124"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="106"/>
+      <c r="R15" s="107"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="119"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="123"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="123"/>
-      <c r="P16" s="123"/>
-      <c r="Q16" s="123"/>
-      <c r="R16" s="124"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="106"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="106"/>
+      <c r="Q16" s="106"/>
+      <c r="R16" s="107"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="124"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="106"/>
+      <c r="O17" s="106"/>
+      <c r="P17" s="106"/>
+      <c r="Q17" s="106"/>
+      <c r="R17" s="107"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="119"/>
-      <c r="C18" s="120"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="123"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="123"/>
-      <c r="R18" s="124"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="106"/>
+      <c r="O18" s="106"/>
+      <c r="P18" s="106"/>
+      <c r="Q18" s="106"/>
+      <c r="R18" s="107"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="119"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="122"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="123"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="123"/>
-      <c r="P19" s="123"/>
-      <c r="Q19" s="123"/>
-      <c r="R19" s="124"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="106"/>
+      <c r="R19" s="107"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="120"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="123"/>
-      <c r="M20" s="123"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="123"/>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="124"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="106"/>
+      <c r="O20" s="106"/>
+      <c r="P20" s="106"/>
+      <c r="Q20" s="106"/>
+      <c r="R20" s="107"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="123"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="123"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="123"/>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="124"/>
+      <c r="B21" s="102"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="106"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="106"/>
+      <c r="Q21" s="106"/>
+      <c r="R21" s="107"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="119"/>
-      <c r="C22" s="120"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="120"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="122"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="123"/>
-      <c r="M22" s="123"/>
-      <c r="N22" s="123"/>
-      <c r="O22" s="123"/>
-      <c r="P22" s="123"/>
-      <c r="Q22" s="123"/>
-      <c r="R22" s="124"/>
+      <c r="B22" s="102"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="102"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="106"/>
+      <c r="O22" s="106"/>
+      <c r="P22" s="106"/>
+      <c r="Q22" s="106"/>
+      <c r="R22" s="107"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3489,6 +3555,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:H21"/>
@@ -3497,78 +3635,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="I22:R22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:O2"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:R4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3581,23 +3647,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="79" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3608,19 +3674,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="115"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3653,14 +3719,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3668,14 +3734,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="125" t="s">
+      <c r="K4" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="127"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="129"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4213,48 +4279,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="87"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="90"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4284,7 +4350,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4302,27 +4368,27 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
+      <c r="B5" s="132" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
+      <c r="K5" s="132"/>
+      <c r="L5" s="132"/>
+      <c r="M5" s="132"/>
+      <c r="N5" s="132"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -4358,7 +4424,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -4376,38 +4442,38 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
-      <c r="I9" s="89"/>
-      <c r="J9" s="89"/>
-      <c r="K9" s="89"/>
-      <c r="L9" s="89"/>
-      <c r="M9" s="89"/>
-      <c r="N9" s="89"/>
+      <c r="B9" s="133" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="89"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
       <c r="O10" s="36"/>
     </row>
     <row r="11" spans="1:15">
@@ -4430,7 +4496,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -4448,115 +4514,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
+      <c r="B13" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="78" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
+      <c r="B14" s="130" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="78" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
+      <c r="B15" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="130"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="78"/>
+      <c r="B16" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
+      <c r="M16" s="130"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="130"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="78" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
+      <c r="B17" s="130" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="130"/>
+      <c r="N17" s="130"/>
+      <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
+      <c r="M18" s="130"/>
+      <c r="N18" s="130"/>
+      <c r="O18" s="130"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
@@ -4578,7 +4644,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
@@ -4597,7 +4663,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4650,7 +4716,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -4669,7 +4735,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4688,7 +4754,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4707,7 +4773,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4742,7 +4808,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -4761,7 +4827,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4780,7 +4846,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4799,7 +4865,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4862,28 +4928,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="131" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4893,17 +4959,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="90"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4933,7 +4999,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4968,12 +5034,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
-      <c r="B6" s="130" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="143" t="s">
-        <v>117</v>
+      <c r="B6" s="136" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="137"/>
+      <c r="D6" s="78" t="s">
+        <v>113</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -4989,12 +5055,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
-      <c r="B7" s="128" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="129"/>
+      <c r="B7" s="134" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="135"/>
       <c r="D7" s="17" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5010,12 +5076,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="128" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="129"/>
+      <c r="B8" s="134" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="135"/>
       <c r="D8" s="17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5472,23 +5538,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8D2F9E-DCA9-4610-96AE-118D7871E7D7}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="10" max="10" width="10.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="84"/>
+      <c r="D1" s="87"/>
       <c r="E1" s="72" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F1" s="72"/>
       <c r="G1" s="72"/>
@@ -5499,27 +5565,27 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="132">
-        <v>46274</v>
-      </c>
-      <c r="O1" s="132"/>
+      <c r="N1" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="O1" s="88"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="87"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="90"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5527,8 +5593,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="142"/>
-      <c r="O2" s="142"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5550,7 +5616,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5586,12 +5652,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="50" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="50" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F6" s="51"/>
       <c r="G6" s="51"/>
@@ -5599,7 +5665,7 @@
       <c r="I6" s="52"/>
       <c r="J6" s="67"/>
       <c r="K6" s="50" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L6" s="56"/>
       <c r="M6" s="71"/>
@@ -5609,12 +5675,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5622,7 +5688,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5632,12 +5698,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5645,7 +5711,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5655,12 +5721,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5668,7 +5734,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5678,20 +5744,20 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="133" t="s">
-        <v>136</v>
-      </c>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="135"/>
+      <c r="E10" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="81"/>
       <c r="K10" s="70" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L10" s="56"/>
       <c r="M10" s="31"/>
@@ -5700,13 +5766,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
-      <c r="B11" s="133" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="144" t="s">
-        <v>138</v>
+      <c r="B11" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="80"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="69" t="s">
+        <v>132</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="55"/>
@@ -5714,7 +5780,7 @@
       <c r="I11" s="55"/>
       <c r="J11" s="56"/>
       <c r="K11" s="70" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="L11" s="56"/>
       <c r="M11" s="31"/>
@@ -5741,7 +5807,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="36" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C13" s="36"/>
       <c r="D13" s="36"/>
@@ -5749,7 +5815,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="43" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -5768,7 +5834,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
@@ -5776,7 +5842,7 @@
       <c r="F15" s="58"/>
       <c r="G15" s="58"/>
       <c r="H15" s="58" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="I15" s="58"/>
       <c r="J15" s="43"/>
@@ -5789,7 +5855,7 @@
     <row r="16" spans="1:15">
       <c r="A16" s="36"/>
       <c r="B16" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C16" s="58"/>
       <c r="D16" s="58"/>
@@ -5825,7 +5891,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C18" s="58"/>
       <c r="D18" s="58"/>
@@ -5844,7 +5910,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="58" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
@@ -5852,7 +5918,7 @@
       <c r="F19" s="43"/>
       <c r="G19" s="43"/>
       <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
+      <c r="I19" s="58"/>
       <c r="J19" s="43"/>
       <c r="K19" s="43"/>
       <c r="L19" s="43"/>
@@ -5862,7 +5928,9 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
-      <c r="B20" s="31"/>
+      <c r="B20" s="7" t="s">
+        <v>136</v>
+      </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
@@ -5879,9 +5947,7 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
-      <c r="B21" s="7" t="s">
-        <v>129</v>
-      </c>
+      <c r="B21" s="7"/>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
       <c r="E21" s="43"/>
@@ -5896,70 +5962,69 @@
       <c r="N21" s="43"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15" ht="18" customHeight="1">
-      <c r="A22" s="45"/>
-      <c r="B22" s="58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
+    <row r="22" spans="1:15">
+      <c r="A22" s="36"/>
+      <c r="B22" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
       <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1">
-      <c r="A23" s="8"/>
+      <c r="A23" s="45"/>
       <c r="B23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
+      <c r="B24" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
       <c r="O24" s="7"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="43" t="s">
-        <v>130</v>
-      </c>
+      <c r="B25" s="58"/>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
       <c r="G25" s="47"/>
       <c r="H25" s="47"/>
       <c r="I25" s="47"/>
@@ -5972,8 +6037,8 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58" t="s">
-        <v>134</v>
+      <c r="B26" s="43" t="s">
+        <v>137</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -5992,7 +6057,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -6010,7 +6075,9 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
+      <c r="B28" s="58" t="s">
+        <v>128</v>
+      </c>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
@@ -6028,7 +6095,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="58" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
@@ -6046,60 +6113,64 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
+      <c r="B30" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
+      <c r="N30" s="47"/>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="47"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="47"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
+      <c r="B32" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
+      <c r="L32" s="47"/>
+      <c r="M32" s="47"/>
+      <c r="N32" s="47"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>133</v>
+      </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -6130,6 +6201,57 @@
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
       <c r="O34" s="7"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="7"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="7"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6153,48 +6275,44 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>32</v>
-      </c>
+      <c r="M1" s="26"/>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
-        <v>46001</v>
-      </c>
+      <c r="O1" s="40"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="90"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6224,7 +6342,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6242,9 +6360,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="31" t="s">
-        <v>46</v>
-      </c>
+      <c r="B5" s="31"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
@@ -6279,7 +6395,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -6297,9 +6413,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="36" t="s">
-        <v>48</v>
-      </c>
+      <c r="B8" s="36"/>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
@@ -6316,9 +6430,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="36" t="s">
-        <v>49</v>
-      </c>
+      <c r="B9" s="36"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -6692,28 +6804,28 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="87"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="87"/>
+      <c r="E1" s="131" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6723,17 +6835,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="90"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6780,23 +6892,23 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="61" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C5" s="62"/>
       <c r="D5" s="61" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" s="62"/>
       <c r="F5" s="61" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I5" s="62"/>
       <c r="J5" s="61" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K5" s="55"/>
       <c r="L5" s="63"/>
@@ -6807,11 +6919,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="54" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="54" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -6819,11 +6931,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -6834,11 +6946,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="54" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E7" s="57"/>
       <c r="F7" s="54">
@@ -6846,11 +6958,11 @@
       </c>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="54" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="55"/>
@@ -6861,11 +6973,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="54" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="54">
@@ -6873,11 +6985,11 @@
       </c>
       <c r="G8" s="57"/>
       <c r="H8" s="54" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="54" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="55"/>
@@ -6888,11 +7000,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="17">
@@ -6900,26 +7012,26 @@
       </c>
       <c r="G9" s="57"/>
       <c r="H9" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I9" s="57"/>
-      <c r="J9" s="133" t="s">
-        <v>89</v>
-      </c>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="135"/>
+      <c r="J9" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="81"/>
       <c r="N9" s="8"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="69" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E10" s="57"/>
       <c r="F10" s="17">
@@ -6927,7 +7039,7 @@
       </c>
       <c r="G10" s="57"/>
       <c r="H10" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="17"/>
@@ -6940,11 +7052,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="17">
@@ -6952,11 +7064,11 @@
       </c>
       <c r="G11" s="57"/>
       <c r="H11" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I11" s="57"/>
       <c r="J11" s="17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -6967,11 +7079,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="17">
@@ -6979,11 +7091,11 @@
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I12" s="57"/>
       <c r="J12" s="17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -6994,11 +7106,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="17">
@@ -7006,7 +7118,7 @@
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I13" s="57"/>
       <c r="J13" s="17"/>
@@ -7019,11 +7131,11 @@
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="76" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C14" s="75"/>
       <c r="D14" s="17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="17">
@@ -7031,26 +7143,26 @@
       </c>
       <c r="G14" s="57"/>
       <c r="H14" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I14" s="57"/>
-      <c r="J14" s="136" t="s">
-        <v>91</v>
-      </c>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="138"/>
+      <c r="J14" s="138" t="s">
+        <v>87</v>
+      </c>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="140"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="76" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C15" s="75"/>
       <c r="D15" s="17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E15" s="57"/>
       <c r="F15" s="17">
@@ -7058,15 +7170,15 @@
       </c>
       <c r="G15" s="57"/>
       <c r="H15" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I15" s="57"/>
-      <c r="J15" s="139" t="s">
-        <v>92</v>
-      </c>
-      <c r="K15" s="140"/>
-      <c r="L15" s="140"/>
-      <c r="M15" s="141"/>
+      <c r="J15" s="141" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="143"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
@@ -7415,28 +7527,28 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="84"/>
-      <c r="E1" s="85" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="87"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="87"/>
+      <c r="E1" s="131" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="90"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7446,17 +7558,17 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="87"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="90"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7506,21 +7618,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D5" s="52"/>
       <c r="E5" s="66"/>
       <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I5" s="66"/>
       <c r="J5" s="52"/>
       <c r="K5" s="52"/>
       <c r="L5" s="67"/>
       <c r="M5" s="61" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
@@ -7531,26 +7643,26 @@
         <v>1</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6" s="52"/>
       <c r="E6" s="23"/>
       <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="67"/>
       <c r="M6" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N6" s="63"/>
       <c r="O6" s="56"/>
       <c r="P6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -7559,21 +7671,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23"/>
       <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="67"/>
       <c r="M7" s="77" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N7" s="55"/>
       <c r="O7" s="56"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5A4285-6BAC-4F9F-956A-FD92F0712E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9900862F-2F2B-46EF-9965-A899576A3474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="158">
   <si>
     <t>要件定義</t>
   </si>
@@ -294,56 +294,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>生年月日</t>
-    <rPh sb="0" eb="4">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>データ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>メールアドレス</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>電話番号</t>
-    <rPh sb="0" eb="4">
-      <t>デンワバンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>郵便番号</t>
-    <rPh sb="0" eb="4">
-      <t>ユウビンバンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>住所</t>
-    <rPh sb="0" eb="2">
-      <t>ジュウショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>最終学歴</t>
-    <rPh sb="0" eb="4">
-      <t>サイシュウガクレキ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>希望勤務地</t>
-    <rPh sb="0" eb="5">
-      <t>キボウキンムチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>文字列</t>
     <phoneticPr fontId="13"/>
   </si>
@@ -356,91 +306,6 @@
   </si>
   <si>
     <t>全角</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ラジオボタン</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-年：1946～2026　月：1～12　日：1～31</t>
-    <rPh sb="6" eb="7">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ハイフンなし（ハイフンなしと表示する）</t>
-    <rPh sb="14" eb="16">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-「中学校卒業」「高等学校卒業」「専門学校卒業」
-「短期大学卒業」「四年制大学卒業」「大学院修了」
-「その他」</t>
-    <rPh sb="7" eb="10">
-      <t>チュウガッコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="14" eb="20">
-      <t>コウトウガッコウソツギョウ</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>センモンガッコウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>タンキダイガク</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="39" eb="44">
-      <t>ヨネンセイダイガク</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="48" eb="53">
-      <t>ダイガクインシュウリョウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-「東京」「神奈川」「愛知」「大阪」「福岡」</t>
-    <rPh sb="7" eb="9">
-      <t>トウキョウ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>カナガワ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>アイチ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>オオサカ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>フクオカ</t>
-    </rPh>
     <phoneticPr fontId="13"/>
   </si>
   <si>
@@ -1249,6 +1114,251 @@
   </si>
   <si>
     <t>2026/9/9.10</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>部署</t>
+    <rPh sb="0" eb="2">
+      <t>ブショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>必須</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>半角英数字、＠、．（ドット）、-（ハイフン）</t>
+    <rPh sb="0" eb="2">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>エイスウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>登録日時</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>更新日時</t>
+    <rPh sb="0" eb="4">
+      <t>コウシンニチジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>削除フラグ</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>社員ID</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>自動採番</t>
+    <rPh sb="0" eb="4">
+      <t>ジドウサイバン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>必須</t>
+    <rPh sb="0" eb="2">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>数値</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>初期値：０
+有効：０　無効：１</t>
+    <rPh sb="0" eb="3">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ムコウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>―</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>自動入力</t>
+    <rPh sb="0" eb="2">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>更新時、自動入力</t>
+    <rPh sb="0" eb="3">
+      <t>コウシンジ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>ジドウニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【社員情報】</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【タスク情報】</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ラジオボタン
+男：0　女：1　両方：2</t>
+    <rPh sb="7" eb="8">
+      <t>オトコ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>リョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク詳細</t>
+    <rPh sb="3" eb="5">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>優先度</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>期限</t>
+    <rPh sb="0" eb="2">
+      <t>キゲン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>「営業部」：１「総務部」：２「人事部」：３「経理部」：４「システム部」：５
+「マーケティング部」：６</t>
+    <rPh sb="1" eb="3">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウム</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジンジ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ケイリ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>★：１、★★：２、★★★：３</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ステータス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク名・タスク詳細・優先度（★、★★、★★★）・期限・ステータス（未着手、対応中、確認中、完了、保留）</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>「未着手」：１「対応中」：２
+「確認中」：３「完了」：４「保留」：５</t>
+    <rPh sb="1" eb="4">
+      <t>ミチャクシュ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>タイオウチュウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>カクニンチュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ホリュウ</t>
+    </rPh>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -1742,7 +1852,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1971,15 +2081,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1989,6 +2099,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2007,172 +2126,169 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2583,44 +2699,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="99"/>
-      <c r="B6" s="100"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="101" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="101"/>
-      <c r="L6" s="101"/>
-      <c r="M6" s="101"/>
-      <c r="N6" s="100"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="99"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="94"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="101" t="s">
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="101"/>
-      <c r="N7" s="100"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="99"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="94"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2682,16 +2798,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="92" t="s">
+      <c r="F11" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="93"/>
-      <c r="H11" s="96" t="s">
+      <c r="G11" s="99"/>
+      <c r="H11" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="97"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2704,16 +2820,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="92" t="s">
+      <c r="F12" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="93"/>
-      <c r="H12" s="94">
+      <c r="G12" s="99"/>
+      <c r="H12" s="102">
         <v>46273</v>
       </c>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2726,16 +2842,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="92" t="s">
+      <c r="F13" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="93"/>
-      <c r="H13" s="94">
+      <c r="G13" s="99"/>
+      <c r="H13" s="102">
         <v>46273</v>
       </c>
-      <c r="I13" s="95"/>
-      <c r="J13" s="95"/>
-      <c r="K13" s="95"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2748,14 +2864,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="92" t="s">
+      <c r="F14" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="93"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="97"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -2892,22 +3008,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2920,52 +3036,52 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="116" t="s">
+      <c r="B1" s="104"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="118"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="108"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="123"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="113"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="84"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="121"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="111"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="123"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="113"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -2991,427 +3107,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="125"/>
-      <c r="D4" s="124" t="s">
+      <c r="C4" s="115"/>
+      <c r="D4" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="125"/>
-      <c r="F4" s="124" t="s">
+      <c r="E4" s="115"/>
+      <c r="F4" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="126"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="124" t="s">
+      <c r="G4" s="116"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="126"/>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="125"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="115"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="112"/>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="113"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="106"/>
-      <c r="Q6" s="106"/>
-      <c r="R6" s="107"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="127"/>
+      <c r="N6" s="127"/>
+      <c r="O6" s="127"/>
+      <c r="P6" s="127"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="128"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="107"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="128"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="106"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="106"/>
-      <c r="N8" s="106"/>
-      <c r="O8" s="106"/>
-      <c r="P8" s="106"/>
-      <c r="Q8" s="106"/>
-      <c r="R8" s="107"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="123"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="126"/>
+      <c r="J8" s="127"/>
+      <c r="K8" s="127"/>
+      <c r="L8" s="127"/>
+      <c r="M8" s="127"/>
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="128"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="106"/>
-      <c r="O9" s="106"/>
-      <c r="P9" s="106"/>
-      <c r="Q9" s="106"/>
-      <c r="R9" s="107"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="128"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="106"/>
-      <c r="R10" s="107"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127"/>
+      <c r="L10" s="127"/>
+      <c r="M10" s="127"/>
+      <c r="N10" s="127"/>
+      <c r="O10" s="127"/>
+      <c r="P10" s="127"/>
+      <c r="Q10" s="127"/>
+      <c r="R10" s="128"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="102"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="106"/>
-      <c r="O11" s="106"/>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="106"/>
-      <c r="R11" s="107"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="128"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="102"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="107"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
+      <c r="M12" s="127"/>
+      <c r="N12" s="127"/>
+      <c r="O12" s="127"/>
+      <c r="P12" s="127"/>
+      <c r="Q12" s="127"/>
+      <c r="R12" s="128"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="107"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="127"/>
+      <c r="O13" s="127"/>
+      <c r="P13" s="127"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="128"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="106"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="106"/>
-      <c r="Q14" s="106"/>
-      <c r="R14" s="107"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="127"/>
+      <c r="L14" s="127"/>
+      <c r="M14" s="127"/>
+      <c r="N14" s="127"/>
+      <c r="O14" s="127"/>
+      <c r="P14" s="127"/>
+      <c r="Q14" s="127"/>
+      <c r="R14" s="128"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="102"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="107"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="127"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="127"/>
+      <c r="P15" s="127"/>
+      <c r="Q15" s="127"/>
+      <c r="R15" s="128"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="102"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="106"/>
-      <c r="R16" s="107"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="127"/>
+      <c r="M16" s="127"/>
+      <c r="N16" s="127"/>
+      <c r="O16" s="127"/>
+      <c r="P16" s="127"/>
+      <c r="Q16" s="127"/>
+      <c r="R16" s="128"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="106"/>
-      <c r="R17" s="107"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="128"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="102"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="106"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="106"/>
-      <c r="Q18" s="106"/>
-      <c r="R18" s="107"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="127"/>
+      <c r="K18" s="127"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="127"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="127"/>
+      <c r="R18" s="128"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="102"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="107"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="127"/>
+      <c r="K19" s="127"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="127"/>
+      <c r="P19" s="127"/>
+      <c r="Q19" s="127"/>
+      <c r="R19" s="128"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="102"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="106"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="106"/>
-      <c r="N20" s="106"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="106"/>
-      <c r="Q20" s="106"/>
-      <c r="R20" s="107"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="126"/>
+      <c r="J20" s="127"/>
+      <c r="K20" s="127"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="127"/>
+      <c r="N20" s="127"/>
+      <c r="O20" s="127"/>
+      <c r="P20" s="127"/>
+      <c r="Q20" s="127"/>
+      <c r="R20" s="128"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="102"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="106"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
-      <c r="Q21" s="106"/>
-      <c r="R21" s="107"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="127"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="127"/>
+      <c r="O21" s="127"/>
+      <c r="P21" s="127"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="128"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="106"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="106"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="107"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="127"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="127"/>
+      <c r="N22" s="127"/>
+      <c r="O22" s="127"/>
+      <c r="P22" s="127"/>
+      <c r="Q22" s="127"/>
+      <c r="R22" s="128"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3555,6 +3671,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:O2"/>
     <mergeCell ref="Q1:R1"/>
@@ -3563,78 +3751,6 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:R22"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3647,23 +3763,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="82" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3674,19 +3790,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3719,14 +3835,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="127" t="s">
+      <c r="B4" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="129"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="131"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3734,14 +3850,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="127" t="s">
+      <c r="K4" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="129"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="131"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4279,23 +4395,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="86" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="131" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4306,21 +4422,21 @@
         <v>3</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4368,27 +4484,27 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="132" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
-      <c r="J5" s="132"/>
-      <c r="K5" s="132"/>
-      <c r="L5" s="132"/>
-      <c r="M5" s="132"/>
-      <c r="N5" s="132"/>
+      <c r="B5" s="133" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -4442,38 +4558,38 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="133" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="133"/>
+      <c r="B9" s="134" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="134"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="134"/>
+      <c r="N9" s="134"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="133"/>
-      <c r="K10" s="133"/>
-      <c r="L10" s="133"/>
-      <c r="M10" s="133"/>
-      <c r="N10" s="133"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="134"/>
+      <c r="K10" s="134"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="134"/>
+      <c r="N10" s="134"/>
       <c r="O10" s="36"/>
     </row>
     <row r="11" spans="1:15">
@@ -4514,115 +4630,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="132"/>
+      <c r="O13" s="132"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="130" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
+      <c r="B14" s="132" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="132"/>
+      <c r="M14" s="132"/>
+      <c r="N14" s="132"/>
+      <c r="O14" s="132"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="130" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
+      <c r="B15" s="132" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="132"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="132"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="130" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
+      <c r="B16" s="132" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="132"/>
+      <c r="M16" s="132"/>
+      <c r="N16" s="132"/>
+      <c r="O16" s="132"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="130" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
+      <c r="B17" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
-      <c r="M18" s="130"/>
-      <c r="N18" s="130"/>
-      <c r="O18" s="130"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="132"/>
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
@@ -4663,7 +4779,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4735,7 +4851,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4754,7 +4870,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4773,7 +4889,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4827,7 +4943,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4846,7 +4962,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4865,7 +4981,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4928,23 +5044,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="86" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="131" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4959,17 +5075,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5034,12 +5150,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="137"/>
-      <c r="D6" s="78" t="s">
-        <v>113</v>
+      <c r="C6" s="138"/>
+      <c r="D6" s="77" t="s">
+        <v>100</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -5055,12 +5171,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
-      <c r="B7" s="134" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="135"/>
+      <c r="B7" s="135" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="136"/>
       <c r="D7" s="17" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5076,12 +5192,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="135"/>
+      <c r="C8" s="136"/>
       <c r="D8" s="17" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5545,14 +5661,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="86" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="87"/>
+      <c r="D1" s="90"/>
       <c r="E1" s="72" t="s">
         <v>67</v>
       </c>
@@ -5570,22 +5686,22 @@
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="O1" s="88"/>
+      <c r="N1" s="139" t="s">
+        <v>129</v>
+      </c>
+      <c r="O1" s="139"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="93"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5593,8 +5709,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5675,12 +5791,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5688,7 +5804,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5698,12 +5814,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5711,7 +5827,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5721,12 +5837,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5734,7 +5850,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5744,12 +5860,12 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="79" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F10" s="80"/>
       <c r="G10" s="80"/>
@@ -5757,7 +5873,7 @@
       <c r="I10" s="80"/>
       <c r="J10" s="81"/>
       <c r="K10" s="70" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L10" s="56"/>
       <c r="M10" s="31"/>
@@ -5767,12 +5883,12 @@
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
       <c r="B11" s="79" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C11" s="80"/>
       <c r="D11" s="81"/>
       <c r="E11" s="69" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="55"/>
@@ -5780,7 +5896,7 @@
       <c r="I11" s="55"/>
       <c r="J11" s="56"/>
       <c r="K11" s="70" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L11" s="56"/>
       <c r="M11" s="31"/>
@@ -5815,7 +5931,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="43" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -5834,7 +5950,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
@@ -5842,7 +5958,7 @@
       <c r="F15" s="58"/>
       <c r="G15" s="58"/>
       <c r="H15" s="58" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="I15" s="58"/>
       <c r="J15" s="43"/>
@@ -5891,7 +6007,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="7" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C18" s="58"/>
       <c r="D18" s="58"/>
@@ -5910,7 +6026,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="58" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
@@ -5929,7 +6045,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="7" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -5965,7 +6081,7 @@
     <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="7" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -6003,7 +6119,7 @@
     <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="58" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -6038,7 +6154,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="43" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -6057,7 +6173,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -6076,7 +6192,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
@@ -6095,7 +6211,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="58" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
@@ -6114,7 +6230,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="58" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C30" s="47"/>
       <c r="D30" s="47"/>
@@ -6150,7 +6266,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="58" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C32" s="47"/>
       <c r="D32" s="47"/>
@@ -6169,7 +6285,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6275,23 +6391,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="86" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="131" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6302,17 +6418,17 @@
       <c r="O1" s="40"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6802,50 +6918,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140C4B60-E55A-4E72-B14E-C7619F01C68D}">
   <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="86" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="131" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="40">
-        <v>46268</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6874,6 +6993,817 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
+      <c r="B4" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="8"/>
+      <c r="B5" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="62"/>
+      <c r="F5" s="61" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="62"/>
+      <c r="H5" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="62"/>
+      <c r="J5" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="55"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="8"/>
+      <c r="B6" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="57"/>
+      <c r="F6" s="54">
+        <v>100</v>
+      </c>
+      <c r="G6" s="57"/>
+      <c r="H6" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="57"/>
+      <c r="J6" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="K6" s="55"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="36"/>
+      <c r="B7" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="54">
+        <v>100</v>
+      </c>
+      <c r="G7" s="57"/>
+      <c r="H7" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="57"/>
+      <c r="J7" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="55"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="36"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="36"/>
+      <c r="B8" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="57"/>
+      <c r="D8" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="57"/>
+      <c r="F8" s="54">
+        <v>100</v>
+      </c>
+      <c r="G8" s="57"/>
+      <c r="H8" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="57"/>
+      <c r="J8" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="23"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+    </row>
+    <row r="9" spans="1:15" ht="36" customHeight="1">
+      <c r="A9" s="36"/>
+      <c r="B9" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="57"/>
+      <c r="F9" s="54">
+        <v>1</v>
+      </c>
+      <c r="G9" s="57"/>
+      <c r="H9" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="57"/>
+      <c r="J9" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="145"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="36"/>
+      <c r="B10" s="54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="57"/>
+      <c r="F10" s="54">
+        <v>100</v>
+      </c>
+      <c r="G10" s="57"/>
+      <c r="H10" s="54" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="78" t="s">
+        <v>133</v>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+    </row>
+    <row r="11" spans="1:15" ht="54" customHeight="1">
+      <c r="A11" s="36"/>
+      <c r="B11" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="57"/>
+      <c r="F11" s="17">
+        <v>100</v>
+      </c>
+      <c r="G11" s="57"/>
+      <c r="H11" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="82" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="84"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="36"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="36"/>
+      <c r="B12" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="57"/>
+      <c r="D12" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="57"/>
+      <c r="F12" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="57"/>
+      <c r="H12" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I12" s="57"/>
+      <c r="J12" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="36"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="36"/>
+      <c r="B13" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="56"/>
+      <c r="D13" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="57"/>
+      <c r="F13" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" s="57"/>
+      <c r="H13" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I13" s="57"/>
+      <c r="J13" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+    </row>
+    <row r="14" spans="1:15" ht="36" customHeight="1">
+      <c r="A14" s="36"/>
+      <c r="B14" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="75"/>
+      <c r="D14" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="57"/>
+      <c r="F14" s="17">
+        <v>1</v>
+      </c>
+      <c r="G14" s="57"/>
+      <c r="H14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="57"/>
+      <c r="J14" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="36"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="141"/>
+      <c r="M15" s="141"/>
+      <c r="N15" s="142"/>
+      <c r="O15" s="43"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="36"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="36"/>
+      <c r="B17" s="43" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="36"/>
+      <c r="B18" s="61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="62"/>
+      <c r="F18" s="61" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="62"/>
+      <c r="H18" s="61" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="62"/>
+      <c r="J18" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="55"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="36"/>
+      <c r="B19" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="57"/>
+      <c r="D19" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="57"/>
+      <c r="F19" s="54">
+        <v>100</v>
+      </c>
+      <c r="G19" s="57"/>
+      <c r="H19" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="57"/>
+      <c r="J19" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="55"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="36"/>
+      <c r="B20" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="54">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="57"/>
+      <c r="H20" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="57"/>
+      <c r="J20" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="23"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+    </row>
+    <row r="21" spans="1:15" ht="36" customHeight="1">
+      <c r="A21" s="36"/>
+      <c r="B21" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="57"/>
+      <c r="D21" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="54">
+        <v>1</v>
+      </c>
+      <c r="G21" s="57"/>
+      <c r="H21" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="57"/>
+      <c r="J21" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" s="23"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+    </row>
+    <row r="22" spans="1:15" ht="18" customHeight="1">
+      <c r="A22" s="45"/>
+      <c r="B22" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="57"/>
+      <c r="D22" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="57"/>
+      <c r="F22" s="54">
+        <v>8</v>
+      </c>
+      <c r="G22" s="57"/>
+      <c r="H22" s="54" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+    </row>
+    <row r="23" spans="1:15" ht="36" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="57"/>
+      <c r="D23" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="57"/>
+      <c r="F23" s="17">
+        <v>1</v>
+      </c>
+      <c r="G23" s="57"/>
+      <c r="H23" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="J23" s="82" t="s">
+        <v>157</v>
+      </c>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="8"/>
+      <c r="B24" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="57"/>
+      <c r="D24" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="57"/>
+      <c r="F24" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="57"/>
+      <c r="H24" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="57"/>
+      <c r="J24" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+    </row>
+    <row r="25" spans="1:15" ht="18" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="56"/>
+      <c r="D25" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="57"/>
+      <c r="F25" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="57"/>
+      <c r="H25" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="57"/>
+      <c r="J25" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+    </row>
+    <row r="26" spans="1:15" ht="36" customHeight="1">
+      <c r="A26" s="8"/>
+      <c r="B26" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="75"/>
+      <c r="D26" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="57"/>
+      <c r="F26" s="17">
+        <v>1</v>
+      </c>
+      <c r="G26" s="57"/>
+      <c r="H26" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="57"/>
+      <c r="J26" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="K26" s="80"/>
+      <c r="L26" s="80"/>
+      <c r="M26" s="81"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="8"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="8"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="8"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:K2"/>
+    <mergeCell ref="J11:M11"/>
+  </mergeCells>
+  <phoneticPr fontId="13"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B52A5B-90BF-4339-BD21-5A13EC799265}">
+  <dimension ref="A1:P34"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="20">
+      <c r="A1" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="40">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="20">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="59"/>
+      <c r="N2" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="26"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="36"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="8"/>
       <c r="B4" s="36"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6889,300 +7819,221 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="8"/>
-      <c r="B5" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="61" t="s">
-        <v>49</v>
-      </c>
+      <c r="B5" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="52"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="52"/>
       <c r="G5" s="62"/>
       <c r="H5" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="62"/>
-      <c r="J5" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="8"/>
-    </row>
-    <row r="6" spans="1:15">
+        <v>56</v>
+      </c>
+      <c r="I5" s="66"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="61" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="63"/>
+      <c r="O5" s="57"/>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="36"/>
-      <c r="B6" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="54">
-        <v>100</v>
-      </c>
+      <c r="B6" s="68">
+        <v>1</v>
+      </c>
+      <c r="C6" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="52"/>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="23"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="63"/>
+      <c r="O6" s="56"/>
+      <c r="P6" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="55"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="36"/>
-    </row>
-    <row r="7" spans="1:15">
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="36"/>
-      <c r="B7" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="54">
-        <v>100</v>
-      </c>
+      <c r="B7" s="68">
+        <v>2</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="52"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="52"/>
       <c r="G7" s="57"/>
       <c r="H7" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="57"/>
-      <c r="J7" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-    </row>
-    <row r="8" spans="1:15">
+        <v>81</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="N7" s="55"/>
+      <c r="O7" s="56"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="36"/>
-      <c r="B8" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="54">
-        <v>1</v>
-      </c>
+      <c r="B8" s="68"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="55"/>
       <c r="G8" s="57"/>
-      <c r="H8" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="57"/>
-      <c r="J8" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-    </row>
-    <row r="9" spans="1:15" ht="36" customHeight="1">
+      <c r="H8" s="54"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="52"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="56"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="36"/>
-      <c r="B9" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="17">
-        <v>8</v>
-      </c>
+      <c r="B9" s="68"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="57"/>
-      <c r="H9" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="57"/>
-      <c r="J9" s="79" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="80"/>
-      <c r="L9" s="80"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="H9" s="17"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="56"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="36"/>
-      <c r="B10" s="69" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="17">
-        <v>100</v>
-      </c>
-      <c r="G10" s="57"/>
-      <c r="H10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="57"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="36"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" s="36"/>
-      <c r="B11" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="57"/>
-      <c r="F11" s="17">
-        <v>11</v>
-      </c>
-      <c r="G11" s="57"/>
-      <c r="H11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="57"/>
-      <c r="J11" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="57"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" s="36"/>
-      <c r="B12" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="57"/>
-      <c r="F12" s="17">
-        <v>7</v>
-      </c>
-      <c r="G12" s="57"/>
-      <c r="H12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="57"/>
-      <c r="J12" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="57"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" s="36"/>
-      <c r="B13" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="57"/>
-      <c r="F13" s="17">
-        <v>100</v>
-      </c>
-      <c r="G13" s="57"/>
-      <c r="H13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="57"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="57"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:15" ht="54" customHeight="1">
+    <row r="14" spans="1:16">
       <c r="A14" s="36"/>
-      <c r="B14" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="75"/>
-      <c r="D14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="57"/>
-      <c r="F14" s="17">
-        <v>10</v>
-      </c>
-      <c r="G14" s="57"/>
-      <c r="H14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="57"/>
-      <c r="J14" s="138" t="s">
-        <v>87</v>
-      </c>
-      <c r="K14" s="139"/>
-      <c r="L14" s="139"/>
-      <c r="M14" s="140"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:15" ht="36" customHeight="1">
+    <row r="15" spans="1:16">
       <c r="A15" s="36"/>
-      <c r="B15" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="75"/>
-      <c r="D15" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="57"/>
-      <c r="F15" s="17">
-        <v>3</v>
-      </c>
-      <c r="G15" s="57"/>
-      <c r="H15" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" s="57"/>
-      <c r="J15" s="141" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="142"/>
-      <c r="L15" s="142"/>
-      <c r="M15" s="143"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" s="36"/>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -7192,10 +8043,10 @@
       <c r="G16" s="43"/>
       <c r="H16" s="43"/>
       <c r="I16" s="43"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="57"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
@@ -7506,650 +8357,6 @@
       <c r="O34" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:K2"/>
-  </mergeCells>
-  <phoneticPr fontId="13"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B52A5B-90BF-4339-BD21-5A13EC799265}">
-  <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData>
-    <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="86" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="131" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="O1" s="40">
-        <v>46268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="59"/>
-      <c r="N2" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="26"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="36"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="8"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="8"/>
-      <c r="B5" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="66"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="N5" s="63"/>
-      <c r="O5" s="57"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="36"/>
-      <c r="B6" s="68">
-        <v>1</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="N6" s="63"/>
-      <c r="O6" s="56"/>
-      <c r="P6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="36"/>
-      <c r="B7" s="68">
-        <v>2</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="N7" s="55"/>
-      <c r="O7" s="56"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="36"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="56"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="36"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="67"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="56"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="36"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="36"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="36"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-    </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-    </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-    </row>
-  </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9900862F-2F2B-46EF-9965-A899576A3474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA1FEDF-179D-4F29-90F5-D9604E613998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="8" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="161">
   <si>
     <t>要件定義</t>
   </si>
@@ -312,85 +312,6 @@
     <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>件数増えることでのスケジュール重複</t>
-    <rPh sb="0" eb="3">
-      <t>ケンスウフ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>チョウフク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>要再度対応</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="1" eb="5">
-      <t>サイドタイオウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>メールにて担当者へ通知</t>
-    <rPh sb="5" eb="8">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ツウチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>一覧表示の際のデータ過多</t>
-    <rPh sb="0" eb="4">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>表示に時間がかかる</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ステータスの選択を作り、表示件数を絞る</t>
-    <rPh sb="6" eb="8">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>ヒョウジケンスウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>シボ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>非機能要件</t>
-    <rPh sb="0" eb="3">
-      <t>ヒキノウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウケン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1338,10 +1259,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>タスク名・タスク詳細・優先度（★、★★、★★★）・期限・ステータス（未着手、対応中、確認中、完了、保留）</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>「未着手」：１「対応中」：２
 「確認中」：３「完了」：４「保留」：５</t>
     <rPh sb="1" eb="4">
@@ -1358,6 +1275,134 @@
     </rPh>
     <rPh sb="29" eb="31">
       <t>ホリュウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・ログイン機能をつける</t>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-3．可用性</t>
+    <rPh sb="4" eb="6">
+      <t>カヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・システム稼働時間は8:00～21:00とする</t>
+    <rPh sb="5" eb="9">
+      <t>カドウジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・画面遷移・表示3秒以内</t>
+    <rPh sb="1" eb="5">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ビョウイナイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスク登録の増加によるデータの圧迫</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>アッパク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>表示に時間がかかるのではないか。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タスクステータス・削除フラグの設定による表示件数の限定化</t>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="20" eb="24">
+      <t>ヒョウジケンスウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>入力漏れ</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>入力漏れによる業務漏れ・遅延</t>
+    <rPh sb="0" eb="3">
+      <t>ニュウリョクモ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チエン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>朝礼・ミーティング等で相互確認の徹底</t>
+    <rPh sb="0" eb="2">
+      <t>チョウレイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ソウゴカクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テッテイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1481,15 +1526,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="8"/>
+      <u val="double"/>
+      <sz val="10"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u val="double"/>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1852,7 +1898,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2081,15 +2127,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2099,13 +2154,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2135,34 +2190,70 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2204,42 +2295,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2276,20 +2331,26 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2699,44 +2760,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="94"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="94"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="104"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97" t="s">
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="94"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="105"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="104"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2798,16 +2859,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="98" t="s">
+      <c r="F11" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="99"/>
-      <c r="H11" s="100" t="s">
+      <c r="G11" s="98"/>
+      <c r="H11" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="101"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2820,16 +2881,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="98" t="s">
+      <c r="F12" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="99"/>
-      <c r="H12" s="102">
+      <c r="G12" s="98"/>
+      <c r="H12" s="99">
         <v>46273</v>
       </c>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2842,16 +2903,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="99"/>
-      <c r="H13" s="102">
+      <c r="G13" s="98"/>
+      <c r="H13" s="99">
         <v>46273</v>
       </c>
-      <c r="I13" s="103"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="103"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2864,14 +2925,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="98" t="s">
+      <c r="F14" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="99"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="101"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3008,22 +3069,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3036,52 +3097,52 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="106" t="s">
+      <c r="B1" s="119"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="108"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="123"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="113"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="128"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="87"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="111"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="126"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="113"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="128"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3107,427 +3168,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="115"/>
-      <c r="D4" s="114" t="s">
+      <c r="C4" s="130"/>
+      <c r="D4" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="115"/>
-      <c r="F4" s="114" t="s">
+      <c r="E4" s="130"/>
+      <c r="F4" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="116"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="114" t="s">
+      <c r="G4" s="131"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="115"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="130"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="122"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="118"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
-      <c r="M6" s="127"/>
-      <c r="N6" s="127"/>
-      <c r="O6" s="127"/>
-      <c r="P6" s="127"/>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="128"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="111"/>
+      <c r="P6" s="111"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="112"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="124"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="127"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="128"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="111"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="123"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="127"/>
-      <c r="K8" s="127"/>
-      <c r="L8" s="127"/>
-      <c r="M8" s="127"/>
-      <c r="N8" s="127"/>
-      <c r="O8" s="127"/>
-      <c r="P8" s="127"/>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="128"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="109"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="112"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="123"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="127"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="127"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="127"/>
-      <c r="O9" s="127"/>
-      <c r="P9" s="127"/>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="128"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="112"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="123"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
-      <c r="M10" s="127"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="127"/>
-      <c r="Q10" s="127"/>
-      <c r="R10" s="128"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="109"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="112"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="123"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="128"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="111"/>
+      <c r="O11" s="111"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="112"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="123"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
-      <c r="M12" s="127"/>
-      <c r="N12" s="127"/>
-      <c r="O12" s="127"/>
-      <c r="P12" s="127"/>
-      <c r="Q12" s="127"/>
-      <c r="R12" s="128"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="112"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="123"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="127"/>
-      <c r="P13" s="127"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="128"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="112"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="123"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="127"/>
-      <c r="K14" s="127"/>
-      <c r="L14" s="127"/>
-      <c r="M14" s="127"/>
-      <c r="N14" s="127"/>
-      <c r="O14" s="127"/>
-      <c r="P14" s="127"/>
-      <c r="Q14" s="127"/>
-      <c r="R14" s="128"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="112"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="123"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="127"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="127"/>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127"/>
-      <c r="Q15" s="127"/>
-      <c r="R15" s="128"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="112"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="123"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="127"/>
-      <c r="M16" s="127"/>
-      <c r="N16" s="127"/>
-      <c r="O16" s="127"/>
-      <c r="P16" s="127"/>
-      <c r="Q16" s="127"/>
-      <c r="R16" s="128"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="112"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="123"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="127"/>
-      <c r="R17" s="128"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="108"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="111"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="112"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="123"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="126"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="127"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="127"/>
-      <c r="N18" s="127"/>
-      <c r="O18" s="127"/>
-      <c r="P18" s="127"/>
-      <c r="Q18" s="127"/>
-      <c r="R18" s="128"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="112"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="123"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="127"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="127"/>
-      <c r="N19" s="127"/>
-      <c r="O19" s="127"/>
-      <c r="P19" s="127"/>
-      <c r="Q19" s="127"/>
-      <c r="R19" s="128"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="111"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="112"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="123"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="123"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="126"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="127"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="127"/>
-      <c r="N20" s="127"/>
-      <c r="O20" s="127"/>
-      <c r="P20" s="127"/>
-      <c r="Q20" s="127"/>
-      <c r="R20" s="128"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="112"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="123"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="124"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="127"/>
-      <c r="L21" s="127"/>
-      <c r="M21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="O21" s="127"/>
-      <c r="P21" s="127"/>
-      <c r="Q21" s="127"/>
-      <c r="R21" s="128"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="111"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="112"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="123"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="124"/>
-      <c r="I22" s="126"/>
-      <c r="J22" s="127"/>
-      <c r="K22" s="127"/>
-      <c r="L22" s="127"/>
-      <c r="M22" s="127"/>
-      <c r="N22" s="127"/>
-      <c r="O22" s="127"/>
-      <c r="P22" s="127"/>
-      <c r="Q22" s="127"/>
-      <c r="R22" s="128"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="112"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3671,6 +3732,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:H21"/>
@@ -3679,78 +3812,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="I22:R22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:O2"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:R4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3763,23 +3824,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:17">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
       <c r="N1" s="24" t="s">
         <v>2</v>
       </c>
@@ -3790,19 +3851,19 @@
       <c r="Q1" s="26"/>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
       <c r="N2" s="27" t="s">
         <v>14</v>
       </c>
@@ -3835,14 +3896,14 @@
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="131"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="134"/>
       <c r="H4" s="35" t="s">
         <v>18</v>
       </c>
@@ -3850,14 +3911,14 @@
       <c r="J4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="129" t="s">
+      <c r="K4" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="131"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="134"/>
       <c r="Q4" s="35" t="s">
         <v>18</v>
       </c>
@@ -4395,23 +4456,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="93"/>
+      <c r="E1" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4422,21 +4483,21 @@
         <v>3</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="96"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4484,27 +4545,27 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="133" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
+      <c r="B5" s="136" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="36"/>
       <c r="B6" s="36" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
@@ -4558,38 +4619,38 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
-      <c r="B9" s="134" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="134"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="134"/>
-      <c r="N9" s="134"/>
+      <c r="B9" s="137" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="137"/>
+      <c r="K9" s="137"/>
+      <c r="L9" s="137"/>
+      <c r="M9" s="137"/>
+      <c r="N9" s="137"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="137"/>
+      <c r="L10" s="137"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="137"/>
       <c r="O10" s="36"/>
     </row>
     <row r="11" spans="1:15">
@@ -4630,115 +4691,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="132" t="s">
+      <c r="B13" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="132"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="36"/>
-      <c r="B14" s="132" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="132"/>
-      <c r="O14" s="132"/>
+      <c r="B14" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="135"/>
+      <c r="O14" s="135"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="132" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="132"/>
+      <c r="B15" s="135" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="135"/>
+      <c r="O15" s="135"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="36"/>
-      <c r="B16" s="132" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="132"/>
-      <c r="K16" s="132"/>
-      <c r="L16" s="132"/>
-      <c r="M16" s="132"/>
-      <c r="N16" s="132"/>
-      <c r="O16" s="132"/>
+      <c r="B16" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="135"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="135"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="132" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="132"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="132"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
+      <c r="B17" s="135" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="135"/>
+      <c r="L17" s="135"/>
+      <c r="M17" s="135"/>
+      <c r="N17" s="135"/>
+      <c r="O17" s="135"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="132"/>
-      <c r="K18" s="132"/>
-      <c r="L18" s="132"/>
-      <c r="M18" s="132"/>
-      <c r="N18" s="132"/>
-      <c r="O18" s="132"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
@@ -4779,7 +4840,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="36"/>
       <c r="B21" s="43" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4851,7 +4912,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="46" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -4870,7 +4931,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="46" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -4889,7 +4950,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="46" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -4943,7 +5004,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="48" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4962,7 +5023,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="48" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4981,7 +5042,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="48" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5044,23 +5105,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="93"/>
+      <c r="E1" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -5075,17 +5136,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="96"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5150,12 +5211,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="36"/>
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="138"/>
-      <c r="D6" s="77" t="s">
-        <v>100</v>
+      <c r="C6" s="141"/>
+      <c r="D6" s="76" t="s">
+        <v>93</v>
       </c>
       <c r="E6" s="51"/>
       <c r="F6" s="51"/>
@@ -5171,12 +5232,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
-      <c r="B7" s="135" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="136"/>
+      <c r="B7" s="138" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="139"/>
       <c r="D7" s="17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="55"/>
@@ -5192,12 +5253,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="135" t="s">
+      <c r="B8" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="136"/>
+      <c r="C8" s="139"/>
       <c r="D8" s="17" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5661,14 +5722,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="90"/>
+      <c r="D1" s="93"/>
       <c r="E1" s="72" t="s">
         <v>67</v>
       </c>
@@ -5686,22 +5747,22 @@
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="139" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" s="139"/>
+      <c r="N1" s="142" t="s">
+        <v>122</v>
+      </c>
+      <c r="O1" s="142"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="93"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="96"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5709,8 +5770,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="143"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="41"/>
@@ -5791,12 +5852,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="36"/>
       <c r="B7" s="54" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
       <c r="E7" s="69" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="55"/>
@@ -5804,7 +5865,7 @@
       <c r="I7" s="55"/>
       <c r="J7" s="56"/>
       <c r="K7" s="70" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L7" s="56"/>
       <c r="M7" s="31"/>
@@ -5814,12 +5875,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
       <c r="B8" s="54" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="55"/>
       <c r="E8" s="69" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="55"/>
@@ -5827,7 +5888,7 @@
       <c r="I8" s="55"/>
       <c r="J8" s="56"/>
       <c r="K8" s="70" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L8" s="56"/>
       <c r="M8" s="31"/>
@@ -5837,12 +5898,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="36"/>
       <c r="B9" s="54" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55"/>
       <c r="E9" s="69" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="55"/>
@@ -5850,7 +5911,7 @@
       <c r="I9" s="55"/>
       <c r="J9" s="56"/>
       <c r="K9" s="70" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L9" s="56"/>
       <c r="M9" s="31"/>
@@ -5860,20 +5921,20 @@
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="17" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="79" t="s">
-        <v>117</v>
-      </c>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="81"/>
+      <c r="E10" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="84"/>
       <c r="K10" s="70" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L10" s="56"/>
       <c r="M10" s="31"/>
@@ -5882,13 +5943,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
-      <c r="B11" s="79" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81"/>
+      <c r="B11" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="83"/>
+      <c r="D11" s="84"/>
       <c r="E11" s="69" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="55"/>
@@ -5896,7 +5957,7 @@
       <c r="I11" s="55"/>
       <c r="J11" s="56"/>
       <c r="K11" s="70" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L11" s="56"/>
       <c r="M11" s="31"/>
@@ -5931,7 +5992,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="36"/>
       <c r="B14" s="43" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
@@ -5950,7 +6011,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="36"/>
       <c r="B15" s="7" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="58"/>
@@ -5958,7 +6019,7 @@
       <c r="F15" s="58"/>
       <c r="G15" s="58"/>
       <c r="H15" s="58" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I15" s="58"/>
       <c r="J15" s="43"/>
@@ -6007,7 +6068,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="36"/>
       <c r="B18" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C18" s="58"/>
       <c r="D18" s="58"/>
@@ -6026,7 +6087,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="58" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
@@ -6045,7 +6106,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -6081,7 +6142,7 @@
     <row r="22" spans="1:15">
       <c r="A22" s="36"/>
       <c r="B22" s="7" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -6119,7 +6180,7 @@
     <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="58" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -6154,7 +6215,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="43" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -6173,7 +6234,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="58" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -6192,7 +6253,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="58" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
@@ -6211,7 +6272,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="58" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C29" s="47"/>
       <c r="D29" s="47"/>
@@ -6230,7 +6291,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="58" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C30" s="47"/>
       <c r="D30" s="47"/>
@@ -6266,7 +6327,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="58" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C32" s="47"/>
       <c r="D32" s="47"/>
@@ -6285,7 +6346,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6389,46 +6450,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D678CDCE-2C5A-4AFB-B9CB-39BA46C32C81}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="93"/>
+      <c r="E1" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="26"/>
+      <c r="M1" s="26" t="s">
+        <v>154</v>
+      </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40"/>
+      <c r="O1" s="40">
+        <v>46282</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="96"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6476,7 +6544,9 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="31"/>
+      <c r="B5" s="31" t="s">
+        <v>153</v>
+      </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
@@ -6529,7 +6599,9 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="36"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="36" t="s">
+        <v>150</v>
+      </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
@@ -6563,7 +6635,9 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
-      <c r="B10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>151</v>
+      </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -6580,7 +6654,9 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="36"/>
-      <c r="B11" s="43"/>
+      <c r="B11" s="43" t="s">
+        <v>152</v>
+      </c>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
@@ -6923,23 +6999,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="93"/>
+      <c r="E1" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6954,17 +7030,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="96"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6994,7 +7070,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7040,11 +7116,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="54" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C6" s="62"/>
       <c r="D6" s="54" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="54">
@@ -7052,11 +7128,11 @@
       </c>
       <c r="G6" s="57"/>
       <c r="H6" s="54" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="I6" s="57"/>
       <c r="J6" s="54" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K6" s="55"/>
       <c r="L6" s="63"/>
@@ -7136,19 +7212,19 @@
         <v>53</v>
       </c>
       <c r="I9" s="57"/>
-      <c r="J9" s="143" t="s">
-        <v>148</v>
-      </c>
-      <c r="K9" s="144"/>
-      <c r="L9" s="144"/>
-      <c r="M9" s="145"/>
+      <c r="J9" s="85" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="87"/>
       <c r="N9" s="36"/>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="36"/>
       <c r="B10" s="54" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="54" t="s">
@@ -7160,11 +7236,11 @@
       </c>
       <c r="G10" s="57"/>
       <c r="H10" s="54" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="78" t="s">
-        <v>133</v>
+      <c r="J10" s="77" t="s">
+        <v>126</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="55"/>
@@ -7175,7 +7251,7 @@
     <row r="11" spans="1:15" ht="54" customHeight="1">
       <c r="A11" s="36"/>
       <c r="B11" s="69" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C11" s="57"/>
       <c r="D11" s="54" t="s">
@@ -7190,35 +7266,35 @@
         <v>53</v>
       </c>
       <c r="I11" s="23"/>
-      <c r="J11" s="82" t="s">
-        <v>153</v>
-      </c>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="84"/>
+      <c r="J11" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="81"/>
       <c r="N11" s="8"/>
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="36"/>
       <c r="B12" s="17" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C12" s="57"/>
       <c r="D12" s="54" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G12" s="57"/>
       <c r="H12" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I12" s="57"/>
       <c r="J12" s="17" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7229,23 +7305,23 @@
     <row r="13" spans="1:15">
       <c r="A13" s="36"/>
       <c r="B13" s="17" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C13" s="56"/>
       <c r="D13" s="54" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E13" s="57"/>
       <c r="F13" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G13" s="57"/>
       <c r="H13" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I13" s="57"/>
       <c r="J13" s="17" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -7256,7 +7332,7 @@
     <row r="14" spans="1:15" ht="36" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="54" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C14" s="75"/>
       <c r="D14" s="54" t="s">
@@ -7271,12 +7347,12 @@
         <v>53</v>
       </c>
       <c r="I14" s="57"/>
-      <c r="J14" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="81"/>
+      <c r="J14" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="84"/>
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
@@ -7290,11 +7366,11 @@
       <c r="G15" s="43"/>
       <c r="H15" s="43"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="142"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
     <row r="16" spans="1:15">
@@ -7317,7 +7393,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="36"/>
       <c r="B17" s="43" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C17" s="43"/>
       <c r="D17" s="43"/>
@@ -7363,7 +7439,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="36"/>
       <c r="B19" s="54" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C19" s="57"/>
       <c r="D19" s="54" t="s">
@@ -7390,7 +7466,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="36"/>
       <c r="B20" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C20" s="57"/>
       <c r="D20" s="54" t="s">
@@ -7402,7 +7478,7 @@
       </c>
       <c r="G20" s="57"/>
       <c r="H20" s="54" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I20" s="57"/>
       <c r="J20" s="54" t="s">
@@ -7417,7 +7493,7 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="36"/>
       <c r="B21" s="54" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="54" t="s">
@@ -7433,7 +7509,7 @@
       </c>
       <c r="I21" s="57"/>
       <c r="J21" s="54" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="55"/>
@@ -7444,11 +7520,11 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="45"/>
       <c r="B22" s="54" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C22" s="57"/>
       <c r="D22" s="54" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E22" s="57"/>
       <c r="F22" s="54">
@@ -7456,10 +7532,10 @@
       </c>
       <c r="G22" s="57"/>
       <c r="H22" s="54" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I22" s="23"/>
-      <c r="J22" s="78"/>
+      <c r="J22" s="77"/>
       <c r="K22" s="23"/>
       <c r="L22" s="55"/>
       <c r="M22" s="56"/>
@@ -7469,7 +7545,7 @@
     <row r="23" spans="1:15" ht="36" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="69" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C23" s="57"/>
       <c r="D23" s="54" t="s">
@@ -7484,35 +7560,35 @@
         <v>53</v>
       </c>
       <c r="I23" s="23"/>
-      <c r="J23" s="82" t="s">
-        <v>157</v>
-      </c>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="84"/>
+      <c r="J23" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="80"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="81"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="17" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C24" s="57"/>
       <c r="D24" s="54" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E24" s="57"/>
       <c r="F24" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G24" s="57"/>
       <c r="H24" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I24" s="57"/>
       <c r="J24" s="17" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -7523,23 +7599,23 @@
     <row r="25" spans="1:15" ht="18" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="17" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C25" s="56"/>
       <c r="D25" s="54" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E25" s="57"/>
       <c r="F25" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G25" s="57"/>
       <c r="H25" s="17" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I25" s="57"/>
       <c r="J25" s="17" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
@@ -7550,7 +7626,7 @@
     <row r="26" spans="1:15" ht="36" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="54" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C26" s="75"/>
       <c r="D26" s="54" t="s">
@@ -7565,12 +7641,12 @@
         <v>53</v>
       </c>
       <c r="I26" s="57"/>
-      <c r="J26" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="81"/>
+      <c r="J26" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="84"/>
       <c r="N26" s="58"/>
       <c r="O26" s="58"/>
     </row>
@@ -7627,9 +7703,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="8" t="s">
-        <v>156</v>
-      </c>
+      <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
@@ -7732,25 +7806,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B52A5B-90BF-4339-BD21-5A13EC799265}">
   <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="93"/>
+      <c r="E1" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="96"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -7761,21 +7838,21 @@
         <v>3</v>
       </c>
       <c r="O1" s="40">
-        <v>46268</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="96"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7844,75 +7921,75 @@
       <c r="N5" s="63"/>
       <c r="O5" s="57"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="36" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="68">
         <v>1</v>
       </c>
-      <c r="C6" s="54" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="63"/>
-      <c r="O6" s="56"/>
-      <c r="P6" t="s">
-        <v>83</v>
-      </c>
+      <c r="C6" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="144"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="144"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="145"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="144"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="79" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="80"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="147"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="36"/>
       <c r="B7" s="68">
         <v>2</v>
       </c>
-      <c r="C7" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="N7" s="55"/>
-      <c r="O7" s="56"/>
+      <c r="C7" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="144"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="I7" s="145"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="144"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="148" t="s">
+        <v>160</v>
+      </c>
+      <c r="N7" s="149"/>
+      <c r="O7" s="150"/>
+      <c r="P7" s="147"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="36"/>
       <c r="B8" s="68"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="56"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="144"/>
+      <c r="L8" s="146"/>
+      <c r="M8" s="77"/>
+      <c r="N8" s="145"/>
+      <c r="O8" s="78"/>
+      <c r="P8" s="147"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="36"/>
@@ -8357,7 +8434,9 @@
       <c r="O34" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M7:O7"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:K1"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA1FEDF-179D-4F29-90F5-D9604E613998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE55709-36C2-485F-BC82-D876A42A0F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="8" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="192">
   <si>
     <t>要件定義</t>
   </si>
@@ -89,40 +89,19 @@
     <t>タイトル</t>
   </si>
   <si>
-    <t>ページ</t>
-  </si>
-  <si>
     <t>第1章</t>
   </si>
   <si>
-    <t>要求概要</t>
-  </si>
-  <si>
     <t>第4章</t>
   </si>
   <si>
-    <t>システムの背景と目的</t>
-  </si>
-  <si>
     <t>用語の定義</t>
   </si>
   <si>
     <t>業務の概要</t>
   </si>
   <si>
-    <t>現状の課題と改善案</t>
-  </si>
-  <si>
-    <t>基本要件と優先順位</t>
-  </si>
-  <si>
     <t>第2章</t>
-  </si>
-  <si>
-    <t>システムの要件</t>
-  </si>
-  <si>
-    <t>システム機能要件</t>
   </si>
   <si>
     <t>第3章</t>
@@ -312,6 +291,16 @@
     <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件</t>
+    <rPh sb="0" eb="3">
+      <t>ヒキノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1403,6 +1392,274 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>テッテイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件（1-3まで）</t>
+    <rPh sb="0" eb="4">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>「業務要件（1-4以降）」、「利用者・権限」、「機能要件（3-1）」作成</t>
+    <rPh sb="1" eb="5">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>「機能要件（3-2以降）」作成</t>
+    <rPh sb="9" eb="11">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>「データ項目定義」作成</t>
+    <rPh sb="4" eb="8">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>「非機能要件」、「リスク・課題」作成</t>
+    <rPh sb="1" eb="6">
+      <t>ヒキノウヨウケン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件</t>
+    <rPh sb="0" eb="4">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第4章</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の背景</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>性能要件</t>
+    <rPh sb="0" eb="4">
+      <t>セイノウヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の目的</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>セキュリティ要件</t>
+    <rPh sb="6" eb="8">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の範囲</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-4</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>現状の課題</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第5章</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>改善後の姿</t>
+    <rPh sb="0" eb="3">
+      <t>カイゼンゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>5-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ項目定義</t>
+    <rPh sb="3" eb="7">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>利用者・権限</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第6章</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>利用者区分</t>
+    <rPh sb="0" eb="5">
+      <t>リヨウシャクブン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>6-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>リスク・課題</t>
+    <rPh sb="4" eb="6">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能要件</t>
+    <rPh sb="0" eb="4">
+      <t>キノウヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>3-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能一覧</t>
+    <rPh sb="0" eb="4">
+      <t>キノウイチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能詳細</t>
+    <rPh sb="0" eb="4">
+      <t>キノウショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>可用性</t>
+    <rPh sb="0" eb="2">
+      <t>カヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>セイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・【社員情報】</t>
+    <rPh sb="2" eb="6">
+      <t>シャインジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・【タスク情報】</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1898,7 +2155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1989,9 +2246,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2004,9 +2258,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2244,9 +2495,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2351,6 +2599,42 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2760,44 +3044,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="104"/>
-      <c r="B6" s="105"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="104"/>
+      <c r="A6" s="102"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="101"/>
+      <c r="P6" s="102"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="104"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="106" t="s">
+      <c r="A7" s="102"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="102"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2859,16 +3143,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="98"/>
-      <c r="H11" s="101" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2881,16 +3165,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="97" t="s">
+      <c r="F12" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="98"/>
-      <c r="H12" s="99">
+      <c r="G12" s="96"/>
+      <c r="H12" s="97">
         <v>46273</v>
       </c>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="98"/>
+      <c r="K12" s="98"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2903,16 +3187,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="97" t="s">
+      <c r="F13" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="98"/>
-      <c r="H13" s="99">
-        <v>46273</v>
-      </c>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="97">
+        <v>46282</v>
+      </c>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="98"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2925,14 +3209,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="97" t="s">
+      <c r="F14" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="98"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3097,52 +3381,56 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="121" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="123"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="120"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="128"/>
+      <c r="Q1" s="124" t="s">
+        <v>148</v>
+      </c>
+      <c r="R1" s="125"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="90"/>
-      <c r="B2" s="120"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="126"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="123"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="128"/>
+      <c r="Q2" s="154">
+        <v>46282</v>
+      </c>
+      <c r="R2" s="155"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3168,427 +3456,457 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="129" t="s">
+      <c r="C4" s="127"/>
+      <c r="D4" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="130"/>
-      <c r="F4" s="129" t="s">
+      <c r="E4" s="127"/>
+      <c r="F4" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="131"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="129" t="s">
+      <c r="G4" s="128"/>
+      <c r="H4" s="127"/>
+      <c r="I4" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="130"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="128"/>
+      <c r="Q4" s="128"/>
+      <c r="R4" s="127"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="117"/>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="118"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="B5" s="148">
+        <v>46273</v>
+      </c>
+      <c r="C5" s="112"/>
+      <c r="D5" s="111" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="112"/>
+      <c r="F5" s="113" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="114"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="114"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="114"/>
+      <c r="P5" s="114"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="115"/>
+    </row>
+    <row r="6" spans="1:18" ht="54" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="107"/>
-      <c r="C6" s="108"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="107"/>
+      <c r="B6" s="149">
+        <v>46274</v>
+      </c>
+      <c r="C6" s="106"/>
+      <c r="D6" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="106"/>
+      <c r="F6" s="150" t="s">
+        <v>156</v>
+      </c>
       <c r="G6" s="109"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="111"/>
-      <c r="P6" s="111"/>
-      <c r="Q6" s="111"/>
-      <c r="R6" s="112"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="110"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="107"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="107"/>
+      <c r="B7" s="149">
+        <v>46275</v>
+      </c>
+      <c r="C7" s="106"/>
+      <c r="D7" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="106"/>
+      <c r="F7" s="108" t="s">
+        <v>157</v>
+      </c>
       <c r="G7" s="109"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111"/>
-      <c r="R7" s="112"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="110"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="107"/>
+      <c r="B8" s="149">
+        <v>46281</v>
+      </c>
+      <c r="C8" s="106"/>
+      <c r="D8" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="106"/>
+      <c r="F8" s="108" t="s">
+        <v>158</v>
+      </c>
       <c r="G8" s="109"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="111"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="111"/>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="112"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="109"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="110"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="107"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="109"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="112"/>
+      <c r="B9" s="149">
+        <v>46282</v>
+      </c>
+      <c r="C9" s="106"/>
+      <c r="D9" s="105" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="106"/>
+      <c r="F9" s="151" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="152"/>
+      <c r="H9" s="153"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="109"/>
+      <c r="N9" s="109"/>
+      <c r="O9" s="109"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="109"/>
+      <c r="R9" s="110"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="107"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="112"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="109"/>
+      <c r="L10" s="109"/>
+      <c r="M10" s="109"/>
+      <c r="N10" s="109"/>
+      <c r="O10" s="109"/>
+      <c r="P10" s="109"/>
+      <c r="Q10" s="109"/>
+      <c r="R10" s="110"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="107"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="111"/>
-      <c r="P11" s="111"/>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="112"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="109"/>
+      <c r="L11" s="109"/>
+      <c r="M11" s="109"/>
+      <c r="N11" s="109"/>
+      <c r="O11" s="109"/>
+      <c r="P11" s="109"/>
+      <c r="Q11" s="109"/>
+      <c r="R11" s="110"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="107"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="111"/>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="112"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="109"/>
+      <c r="K12" s="109"/>
+      <c r="L12" s="109"/>
+      <c r="M12" s="109"/>
+      <c r="N12" s="109"/>
+      <c r="O12" s="109"/>
+      <c r="P12" s="109"/>
+      <c r="Q12" s="109"/>
+      <c r="R12" s="110"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
-      <c r="R13" s="112"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="109"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="110"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="107"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="112"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="106"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="108"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="109"/>
+      <c r="L14" s="109"/>
+      <c r="M14" s="109"/>
+      <c r="N14" s="109"/>
+      <c r="O14" s="109"/>
+      <c r="P14" s="109"/>
+      <c r="Q14" s="109"/>
+      <c r="R14" s="110"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="107"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="112"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="109"/>
+      <c r="M15" s="109"/>
+      <c r="N15" s="109"/>
+      <c r="O15" s="109"/>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="110"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="107"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="111"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="112"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="109"/>
+      <c r="M16" s="109"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="109"/>
+      <c r="Q16" s="109"/>
+      <c r="R16" s="110"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="107"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="108"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="111"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="111"/>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="112"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="106"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="109"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="109"/>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="110"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="107"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="111"/>
-      <c r="N18" s="111"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="111"/>
-      <c r="Q18" s="111"/>
-      <c r="R18" s="112"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="109"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="109"/>
+      <c r="O18" s="109"/>
+      <c r="P18" s="109"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="110"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="111"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="111"/>
-      <c r="R19" s="112"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="109"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="110"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="111"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="112"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="109"/>
+      <c r="P20" s="109"/>
+      <c r="Q20" s="109"/>
+      <c r="R20" s="110"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="111"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="111"/>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="112"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="109"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="109"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="110"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="107"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="111"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="112"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="107"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="110"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3820,566 +4138,466 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFF7F1E-AE30-4269-AC6F-F8A3C5E0A4BA}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="16" max="16" width="10" style="159" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="88" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="88" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="24" t="s">
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="25" t="s">
+      <c r="N1" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="26"/>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="27" t="s">
+      <c r="P1" s="158">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="29" t="s">
+      <c r="N2" s="28"/>
+      <c r="O2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="30"/>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-    </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="34" t="s">
+      <c r="P2" s="158"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="132" t="s">
+      <c r="B4" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="35" t="s">
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="129" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="131"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="16"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="132" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="133"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="133"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="35" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="16"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="I6" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="156" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="I7" s="156" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="156" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="I8" s="156" t="s">
+        <v>168</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="156" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="I9" s="156" t="s">
+        <v>168</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="156" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="I11" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="35"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="I12" s="157" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="157" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="J14" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="157"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+    </row>
+    <row r="17" spans="1:15" ht="26.5">
+      <c r="A17" s="157" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="157" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+    </row>
+    <row r="18" spans="1:15" ht="26.5">
+      <c r="A18" s="157" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+    </row>
+    <row r="19" spans="1:15" ht="26.5">
+      <c r="A19" s="35"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+    </row>
+    <row r="20" spans="1:15" ht="26.5">
+      <c r="A20" s="35">
+        <v>3.2</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="37">
-        <v>1</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="37" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+    </row>
+    <row r="21" spans="1:15" ht="26.5">
+      <c r="A21" s="35">
+        <v>3.3</v>
+      </c>
+      <c r="B21" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="37">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="37">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="37">
-        <v>2</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="37">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="37">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="37">
-        <v>1.2</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37">
-        <v>3</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="37">
-        <v>4.2</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="37">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="37">
-        <v>4</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="37">
-        <v>4.3</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="37">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="37">
-        <v>1.4</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="37">
-        <v>5</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="37">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="37">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="37">
-        <v>1.5</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="37">
-        <v>6</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="37">
-        <v>4.5</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="37">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="37">
-        <v>7</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="37">
-        <v>2.1</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="37">
-        <v>8</v>
-      </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="37">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37">
-        <v>9</v>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="37">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="37">
-        <v>10</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="37">
-        <v>2.4</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="37">
-        <v>11</v>
-      </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="37">
-        <v>2.5</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="37">
-        <v>12</v>
-      </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="37">
-        <v>13</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-    </row>
-    <row r="19" spans="1:17" ht="26.5">
-      <c r="A19" s="37">
-        <v>3.1</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="37">
-        <v>14</v>
-      </c>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-    </row>
-    <row r="20" spans="1:17" ht="26.5">
-      <c r="A20" s="37">
-        <v>3.2</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37">
-        <v>15</v>
-      </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-    </row>
-    <row r="21" spans="1:17" ht="26.5">
-      <c r="A21" s="37">
-        <v>3.3</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="37">
-        <v>16</v>
-      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-    </row>
-    <row r="22" spans="1:17" ht="26.5">
-      <c r="A22" s="38"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+    </row>
+    <row r="22" spans="1:15" ht="26.5">
+      <c r="A22" s="36"/>
       <c r="B22" s="16"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -4388,35 +4606,31 @@
       <c r="G22" s="16"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-    </row>
-    <row r="23" spans="1:17" ht="26.5">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+    </row>
+    <row r="23" spans="1:15" ht="26.5">
+      <c r="A23" s="36"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="7"/>
       <c r="B24" s="16"/>
       <c r="C24" s="7"/>
@@ -4432,15 +4646,13 @@
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:M2"/>
+    <mergeCell ref="C1:L2"/>
     <mergeCell ref="B4:G4"/>
-    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="J4:O4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4456,48 +4668,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="92" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="94"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40" t="s">
-        <v>99</v>
+      <c r="O1" s="38" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4505,29 +4717,29 @@
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74"/>
+      <c r="O2" s="72"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>32</v>
+      <c r="B4" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4545,63 +4757,63 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="136" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
-      <c r="M5" s="136"/>
-      <c r="N5" s="136"/>
+      <c r="B5" s="133" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="36"/>
-      <c r="B6" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36" t="s">
-        <v>33</v>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -4615,46 +4827,46 @@
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
-      <c r="O8" s="36"/>
+      <c r="O8" s="34"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="137" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="137"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="36"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="134" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
+      <c r="E9" s="134"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="134"/>
+      <c r="J9" s="134"/>
+      <c r="K9" s="134"/>
+      <c r="L9" s="134"/>
+      <c r="M9" s="134"/>
+      <c r="N9" s="134"/>
+      <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
-      <c r="B10" s="137"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="137"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="36"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="134"/>
+      <c r="K10" s="134"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="134"/>
+      <c r="N10" s="134"/>
+      <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -4668,232 +4880,232 @@
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
-      <c r="A13" s="36"/>
-      <c r="B13" s="135" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="132" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="132"/>
+      <c r="O13" s="132"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="135" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="132" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="132"/>
+      <c r="M14" s="132"/>
+      <c r="N14" s="132"/>
+      <c r="O14" s="132"/>
+    </row>
+    <row r="15" spans="1:15" ht="18" customHeight="1">
+      <c r="A15" s="34"/>
+      <c r="B15" s="132" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
+      <c r="M15" s="132"/>
+      <c r="N15" s="132"/>
+      <c r="O15" s="132"/>
+    </row>
+    <row r="16" spans="1:15" ht="18" customHeight="1">
+      <c r="A16" s="34"/>
+      <c r="B16" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="135"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="135"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="135"/>
-      <c r="O14" s="135"/>
-    </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="135" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="135"/>
-      <c r="M15" s="135"/>
-      <c r="N15" s="135"/>
-      <c r="O15" s="135"/>
-    </row>
-    <row r="16" spans="1:15" ht="18" customHeight="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="135" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="135"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="132"/>
+      <c r="M16" s="132"/>
+      <c r="N16" s="132"/>
+      <c r="O16" s="132"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
-      <c r="A17" s="36"/>
-      <c r="B17" s="135" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="135"/>
-      <c r="D17" s="135"/>
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="135"/>
-      <c r="L17" s="135"/>
-      <c r="M17" s="135"/>
-      <c r="N17" s="135"/>
-      <c r="O17" s="135"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="132" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="135"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="135"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="135"/>
-      <c r="O18" s="135"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="132"/>
+      <c r="M18" s="132"/>
+      <c r="N18" s="132"/>
+      <c r="O18" s="132"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -4911,81 +5123,81 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
+      <c r="B25" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
+      <c r="B26" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
+      <c r="B27" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -5003,8 +5215,8 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="48" t="s">
-        <v>89</v>
+      <c r="B30" s="46" t="s">
+        <v>83</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -5022,8 +5234,8 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
-      <c r="B31" s="48" t="s">
-        <v>90</v>
+      <c r="B31" s="46" t="s">
+        <v>84</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -5041,8 +5253,8 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
-      <c r="B32" s="48" t="s">
-        <v>91</v>
+      <c r="B32" s="46" t="s">
+        <v>85</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5060,7 +5272,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
-      <c r="B33" s="48"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -5105,48 +5317,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="94"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="38">
         <v>46274</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5154,29 +5366,29 @@
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74"/>
+      <c r="O2" s="72"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>40</v>
+      <c r="B4" s="34" t="s">
+        <v>33</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5194,86 +5406,86 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="141"/>
-      <c r="D6" s="76" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="36"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="137" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="138"/>
+      <c r="D6" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="34"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="138" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="139"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="135" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="136"/>
       <c r="D7" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="52"/>
+        <v>88</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="50"/>
       <c r="I7" s="23"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="139"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="135" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="136"/>
       <c r="D8" s="17" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="50"/>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
-      <c r="K8" s="57"/>
+      <c r="K8" s="55"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
-      <c r="O8" s="36"/>
+      <c r="O8" s="34"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -5287,10 +5499,10 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -5304,211 +5516,211 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="36"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="44"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="44"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="1:15" ht="26.5">
-      <c r="A22" s="45"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="8"/>
@@ -5529,88 +5741,88 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
@@ -5722,47 +5934,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="92" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="72" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="73"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="91"/>
+      <c r="E1" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="71"/>
       <c r="K1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="142" t="s">
-        <v>122</v>
-      </c>
-      <c r="O1" s="142"/>
+      <c r="N1" s="139" t="s">
+        <v>116</v>
+      </c>
+      <c r="O1" s="139"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="94"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5770,30 +5982,30 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="36"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="34"/>
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>58</v>
+      <c r="B4" s="34" t="s">
+        <v>51</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5811,161 +6023,161 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
       <c r="N5" s="8"/>
       <c r="O5" s="7"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" s="56"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="36"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="54"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="34"/>
       <c r="O6" s="7"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="54" t="s">
+      <c r="A7" s="34"/>
+      <c r="B7" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="70" t="s">
-        <v>102</v>
-      </c>
-      <c r="L7" s="56"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="36"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="34"/>
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="69" t="s">
-        <v>81</v>
+      <c r="A8" s="34"/>
+      <c r="B8" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="67" t="s">
+        <v>75</v>
       </c>
       <c r="F8" s="23"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="70" t="s">
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="54"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="34"/>
+      <c r="B9" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="L8" s="56"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="7"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="69" t="s">
-        <v>107</v>
-      </c>
       <c r="F9" s="23"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="L9" s="56"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="36"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9" s="54"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="34"/>
       <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="17" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="82" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" s="56"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="36"/>
+      <c r="E10" s="80" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="54"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="34"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
-      <c r="B11" s="82" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="83"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="69" t="s">
-        <v>112</v>
+      <c r="A11" s="34"/>
+      <c r="B11" s="80" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="81"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="67" t="s">
+        <v>106</v>
       </c>
       <c r="F11" s="23"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="L11" s="56"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="36"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="54"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="34"/>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -5978,209 +6190,209 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="36"/>
+      <c r="N12" s="34"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="34"/>
+      <c r="B14" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="34"/>
+      <c r="B15" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" s="56"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="34"/>
+      <c r="B16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="7"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="34"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="34"/>
+      <c r="B18" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="34"/>
+      <c r="B19" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="34"/>
+      <c r="B20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="34"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="7"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="34"/>
+      <c r="B22" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="7"/>
+    </row>
+    <row r="23" spans="1:15" ht="18" customHeight="1">
+      <c r="A23" s="43"/>
+      <c r="B23" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="7"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
-      <c r="B15" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="I15" s="58"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="7"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="7"/>
-    </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="7"/>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="7"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="7"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="7"/>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="7"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="7"/>
-    </row>
-    <row r="23" spans="1:15" ht="18" customHeight="1">
-      <c r="A23" s="45"/>
-      <c r="B23" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
       <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
-      <c r="B24" s="58" t="s">
-        <v>119</v>
+      <c r="B24" s="56" t="s">
+        <v>113</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -6198,155 +6410,155 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
       <c r="O25" s="7"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
+      <c r="B26" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
       <c r="O26" s="7"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
+      <c r="B27" s="56" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
       <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
+      <c r="B28" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
       <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="58" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
+      <c r="B29" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
       <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
+      <c r="B30" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
-      <c r="B32" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="47"/>
+      <c r="B32" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6455,78 +6667,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="94"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="38">
         <v>46282</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="59"/>
+      <c r="M2" s="57"/>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>44</v>
+      <c r="B4" s="34" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6544,81 +6756,81 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
+      <c r="B5" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="36"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="36"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="34"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -6631,12 +6843,12 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -6650,145 +6862,145 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
-      <c r="B11" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="41"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="36"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="60"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="58"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
     </row>
     <row r="18" spans="1:15" ht="26.5">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="45"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="8"/>
@@ -6809,88 +7021,88 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="8"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="56"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="8"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="8"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="8"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
@@ -6999,78 +7211,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="92" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="94"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="38">
         <v>46281</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="59"/>
+      <c r="M2" s="57"/>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>139</v>
+      <c r="B4" s="34" t="s">
+        <v>133</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7088,616 +7300,616 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="61" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="62"/>
-      <c r="J5" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="31"/>
+      <c r="B5" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="60"/>
+      <c r="F5" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="60"/>
+      <c r="H5" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="60"/>
+      <c r="J5" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="53"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="30"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
-      <c r="B6" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="54" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="54">
+      <c r="B6" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="55"/>
+      <c r="F6" s="52">
         <v>100</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="54" t="s">
-        <v>131</v>
-      </c>
-      <c r="K6" s="55"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="31"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="55"/>
+      <c r="J6" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="K6" s="53"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="30"/>
       <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="54">
+      <c r="A7" s="34"/>
+      <c r="B7" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="55"/>
+      <c r="F7" s="52">
         <v>100</v>
       </c>
-      <c r="G7" s="57"/>
-      <c r="H7" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="57"/>
-      <c r="J7" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="K7" s="55"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="36"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="55"/>
+      <c r="J7" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="53"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="34"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="54">
+      <c r="A8" s="34"/>
+      <c r="B8" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="55"/>
+      <c r="D8" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="55"/>
+      <c r="F8" s="52">
         <v>100</v>
       </c>
-      <c r="G8" s="57"/>
-      <c r="H8" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="57"/>
-      <c r="J8" s="54" t="s">
-        <v>75</v>
+      <c r="G8" s="55"/>
+      <c r="H8" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="55"/>
+      <c r="J8" s="52" t="s">
+        <v>68</v>
       </c>
       <c r="K8" s="23"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
     </row>
     <row r="9" spans="1:15" ht="36" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="54">
+      <c r="A9" s="34"/>
+      <c r="B9" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="52">
         <v>1</v>
       </c>
-      <c r="G9" s="57"/>
-      <c r="H9" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="57"/>
-      <c r="J9" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="87"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="55"/>
+      <c r="J9" s="83" t="s">
+        <v>135</v>
+      </c>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
-      <c r="B10" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="54">
+      <c r="A10" s="34"/>
+      <c r="B10" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="55"/>
+      <c r="F10" s="52">
         <v>100</v>
       </c>
-      <c r="G10" s="57"/>
-      <c r="H10" s="54" t="s">
-        <v>125</v>
+      <c r="G10" s="55"/>
+      <c r="H10" s="52" t="s">
+        <v>119</v>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="77" t="s">
-        <v>126</v>
+      <c r="J10" s="75" t="s">
+        <v>120</v>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:15" ht="54" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="69" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="57"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="55"/>
       <c r="F11" s="17">
         <v>100</v>
       </c>
-      <c r="G11" s="57"/>
+      <c r="G11" s="55"/>
       <c r="H11" s="17" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I11" s="23"/>
-      <c r="J11" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="K11" s="80"/>
-      <c r="L11" s="80"/>
-      <c r="M11" s="81"/>
+      <c r="J11" s="77" t="s">
+        <v>140</v>
+      </c>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="79"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="57"/>
+        <v>121</v>
+      </c>
+      <c r="C12" s="55"/>
+      <c r="D12" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="55"/>
       <c r="F12" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G12" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="G12" s="55"/>
       <c r="H12" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I12" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="I12" s="55"/>
       <c r="J12" s="17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="57"/>
+      <c r="M12" s="55"/>
       <c r="N12" s="8"/>
-      <c r="O12" s="36"/>
+      <c r="O12" s="34"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="54"/>
+      <c r="D13" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="57"/>
+      <c r="E13" s="55"/>
       <c r="F13" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="G13" s="55"/>
       <c r="H13" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="I13" s="55"/>
       <c r="J13" s="17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
     </row>
     <row r="14" spans="1:15" ht="36" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="75"/>
-      <c r="D14" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="57"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="73"/>
+      <c r="D14" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="55"/>
       <c r="F14" s="17">
         <v>1</v>
       </c>
-      <c r="G14" s="57"/>
+      <c r="G14" s="55"/>
       <c r="H14" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="57"/>
-      <c r="J14" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+        <v>46</v>
+      </c>
+      <c r="I14" s="55"/>
+      <c r="J14" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="61" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="61" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="62"/>
-      <c r="H18" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="62"/>
-      <c r="J18" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="K18" s="55"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="60"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="60"/>
+      <c r="D18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="60"/>
+      <c r="F18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="60"/>
+      <c r="H18" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="60"/>
+      <c r="J18" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="53"/>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="54" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="57"/>
-      <c r="D19" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="57"/>
-      <c r="F19" s="54">
+      <c r="A19" s="34"/>
+      <c r="B19" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="55"/>
+      <c r="D19" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="52">
         <v>100</v>
       </c>
-      <c r="G19" s="57"/>
-      <c r="H19" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="57"/>
-      <c r="J19" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="55"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="55"/>
+      <c r="J19" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="K19" s="53"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="54">
+      <c r="A20" s="34"/>
+      <c r="B20" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="55"/>
+      <c r="D20" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="52">
         <v>1000</v>
       </c>
-      <c r="G20" s="57"/>
-      <c r="H20" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="57"/>
-      <c r="J20" s="54" t="s">
-        <v>75</v>
+      <c r="G20" s="55"/>
+      <c r="H20" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="I20" s="55"/>
+      <c r="J20" s="52" t="s">
+        <v>68</v>
       </c>
       <c r="K20" s="23"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
     </row>
     <row r="21" spans="1:15" ht="36" customHeight="1">
-      <c r="A21" s="36"/>
-      <c r="B21" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="57"/>
-      <c r="D21" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="54">
+      <c r="A21" s="34"/>
+      <c r="B21" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="55"/>
+      <c r="D21" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="52">
         <v>1</v>
       </c>
-      <c r="G21" s="57"/>
-      <c r="H21" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="I21" s="57"/>
-      <c r="J21" s="54" t="s">
-        <v>147</v>
+      <c r="G21" s="55"/>
+      <c r="H21" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="55"/>
+      <c r="J21" s="52" t="s">
+        <v>141</v>
       </c>
       <c r="K21" s="23"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
-      <c r="A22" s="45"/>
-      <c r="B22" s="54" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="57"/>
-      <c r="F22" s="54">
+      <c r="A22" s="43"/>
+      <c r="B22" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="52">
         <v>8</v>
       </c>
-      <c r="G22" s="57"/>
-      <c r="H22" s="54" t="s">
-        <v>125</v>
+      <c r="G22" s="55"/>
+      <c r="H22" s="52" t="s">
+        <v>119</v>
       </c>
       <c r="I22" s="23"/>
-      <c r="J22" s="77"/>
+      <c r="J22" s="75"/>
       <c r="K22" s="23"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
     </row>
     <row r="23" spans="1:15" ht="36" customHeight="1">
       <c r="A23" s="8"/>
-      <c r="B23" s="69" t="s">
-        <v>148</v>
-      </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="57"/>
+      <c r="B23" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" s="55"/>
       <c r="F23" s="17">
         <v>1</v>
       </c>
-      <c r="G23" s="57"/>
+      <c r="G23" s="55"/>
       <c r="H23" s="17" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I23" s="23"/>
-      <c r="J23" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="K23" s="80"/>
-      <c r="L23" s="80"/>
-      <c r="M23" s="81"/>
+      <c r="J23" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="79"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="57"/>
-      <c r="D24" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E24" s="57"/>
+        <v>121</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="55"/>
       <c r="F24" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G24" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="G24" s="55"/>
       <c r="H24" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I24" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="I24" s="55"/>
       <c r="J24" s="17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
     </row>
     <row r="25" spans="1:15" ht="18" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" s="57"/>
+      <c r="E25" s="55"/>
       <c r="F25" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="G25" s="55"/>
       <c r="H25" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="I25" s="57"/>
+        <v>130</v>
+      </c>
+      <c r="I25" s="55"/>
       <c r="J25" s="17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
     </row>
     <row r="26" spans="1:15" ht="36" customHeight="1">
       <c r="A26" s="8"/>
-      <c r="B26" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="75"/>
-      <c r="D26" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="57"/>
+      <c r="B26" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="73"/>
+      <c r="D26" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="55"/>
       <c r="F26" s="17">
         <v>1</v>
       </c>
-      <c r="G26" s="57"/>
+      <c r="G26" s="55"/>
       <c r="H26" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="57"/>
-      <c r="J26" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="84"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
+        <v>46</v>
+      </c>
+      <c r="I26" s="55"/>
+      <c r="J26" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="82"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="56"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="56"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="56"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
     </row>
@@ -7811,77 +8023,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="92" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="96"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="91"/>
+      <c r="E1" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="94"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="38">
         <v>46282</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="59"/>
+      <c r="M2" s="57"/>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="36"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="34"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="8"/>
-      <c r="B4" s="36"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -7898,118 +8110,118 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="8"/>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="66"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="N5" s="63"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="50"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="64"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="61"/>
+      <c r="O5" s="55"/>
     </row>
     <row r="6" spans="1:16" ht="36" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="68">
+      <c r="A6" s="34"/>
+      <c r="B6" s="66">
         <v>1</v>
       </c>
-      <c r="C6" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="144"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="I6" s="145"/>
-      <c r="J6" s="144"/>
-      <c r="K6" s="144"/>
-      <c r="L6" s="146"/>
-      <c r="M6" s="79" t="s">
-        <v>157</v>
-      </c>
-      <c r="N6" s="80"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="147"/>
+      <c r="C6" s="75" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="141"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="142"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="N6" s="78"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="144"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="36"/>
-      <c r="B7" s="68">
+      <c r="A7" s="34"/>
+      <c r="B7" s="66">
         <v>2</v>
       </c>
-      <c r="C7" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="144"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" s="145"/>
-      <c r="J7" s="144"/>
-      <c r="K7" s="144"/>
-      <c r="L7" s="146"/>
-      <c r="M7" s="148" t="s">
-        <v>160</v>
-      </c>
-      <c r="N7" s="149"/>
-      <c r="O7" s="150"/>
-      <c r="P7" s="147"/>
+      <c r="C7" s="75" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="141"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="142"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="143"/>
+      <c r="M7" s="145" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" s="146"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="144"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="36"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="144"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="144"/>
-      <c r="L8" s="146"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="145"/>
-      <c r="O8" s="78"/>
-      <c r="P8" s="147"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="142"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="142"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="144"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="36"/>
-      <c r="B9" s="68"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="66"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="52"/>
+      <c r="D9" s="50"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
-      <c r="G9" s="57"/>
+      <c r="G9" s="55"/>
       <c r="H9" s="17"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="67"/>
+      <c r="J9" s="50"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="65"/>
       <c r="M9" s="17"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="56"/>
+      <c r="O9" s="54"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="36"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -8023,10 +8235,10 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="36"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -8040,211 +8252,211 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="36"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
     </row>
     <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
@@ -8265,88 +8477,88 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="56"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="56"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>

--- a/要件定義書（タスク管理システム）.xlsx
+++ b/要件定義書（タスク管理システム）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE55709-36C2-485F-BC82-D876A42A0F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B5E107-7931-48CF-9E5C-5A54DDA01C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="193">
   <si>
     <t>要件定義</t>
   </si>
@@ -59,9 +59,6 @@
     <t>更新箇所</t>
   </si>
   <si>
-    <t>更新内容</t>
-  </si>
-  <si>
     <t>要件定義書</t>
   </si>
   <si>
@@ -93,12 +90,6 @@
   </si>
   <si>
     <t>第4章</t>
-  </si>
-  <si>
-    <t>用語の定義</t>
-  </si>
-  <si>
-    <t>業務の概要</t>
   </si>
   <si>
     <t>第2章</t>
@@ -352,32 +343,6 @@
     </rPh>
     <rPh sb="17" eb="18">
       <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>本システムの導入により、個人としての管理はもちろん上長からもそれらを見える化を実現し、フォローアップの体制を整える。
-また、各業務の優先順位を明確にして進められるようにする。</t>
-    <rPh sb="51" eb="53">
-      <t>タイセイ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>トトノ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="66" eb="70">
-      <t>ユウセンジュンイ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>メイカク</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t>スス</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1661,6 +1626,33 @@
     <rPh sb="5" eb="7">
       <t>ジョウホウ</t>
     </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>更新内容</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>本システムの導入により、個人としての管理はもちろん上長からもそれらを見える化を実現し、フォローアップの体制を整える。</t>
+  </si>
+  <si>
+    <t>また、各業務の優先順位を明確にして進められるようにする。</t>
+  </si>
+  <si>
+    <t>「業務要件」</t>
+    <rPh sb="1" eb="5">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一部削除（誤植）</t>
     <phoneticPr fontId="13"/>
   </si>
 </sst>
@@ -2387,6 +2379,228 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2396,15 +2610,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2414,183 +2619,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2599,42 +2627,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3044,44 +3036,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="104"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="101"/>
-      <c r="P6" s="102"/>
+      <c r="A6" s="85"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="86"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="85"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="104" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="102"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="88"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="88"/>
+      <c r="L7" s="88"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="86"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="85"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -3143,16 +3135,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="95" t="s">
+      <c r="F11" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="96"/>
-      <c r="H11" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="91" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="92"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3165,16 +3157,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="95" t="s">
+      <c r="F12" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="96"/>
-      <c r="H12" s="97">
+      <c r="G12" s="90"/>
+      <c r="H12" s="93">
         <v>46273</v>
       </c>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -3187,16 +3179,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="95" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="96"/>
-      <c r="H13" s="97">
+      <c r="F13" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="90"/>
+      <c r="H13" s="93">
         <v>46282</v>
       </c>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -3209,14 +3201,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="95" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="96"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
+      <c r="F14" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="90"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3339,7 +3331,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -3353,22 +3345,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3381,56 +3373,56 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="118" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="120"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="103"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="124" t="s">
-        <v>148</v>
-      </c>
-      <c r="R1" s="125"/>
+      <c r="Q1" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="R1" s="108"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="88"/>
-      <c r="B2" s="117"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="122"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="123"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="106"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="154">
+      <c r="Q2" s="109">
         <v>46282</v>
       </c>
-      <c r="R2" s="155"/>
+      <c r="R2" s="110"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3456,457 +3448,465 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="127"/>
-      <c r="D4" s="126" t="s">
+      <c r="C4" s="112"/>
+      <c r="D4" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="127"/>
-      <c r="F4" s="126" t="s">
+      <c r="E4" s="112"/>
+      <c r="F4" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="126" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="127"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113" t="s">
+        <v>188</v>
+      </c>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="113"/>
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="112"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="114">
         <v>46273</v>
       </c>
-      <c r="C5" s="112"/>
-      <c r="D5" s="111" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="112"/>
-      <c r="F5" s="113" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="114"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="114"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="115"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="115"/>
+      <c r="F5" s="117" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="118"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="118"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="119"/>
     </row>
     <row r="6" spans="1:18" ht="54" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="149">
+      <c r="B6" s="120">
         <v>46274</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="106"/>
-      <c r="F6" s="150" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="109"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109"/>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="109"/>
-      <c r="R6" s="110"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="121"/>
+      <c r="F6" s="123" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="125"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="149">
+      <c r="B7" s="120">
         <v>46275</v>
       </c>
-      <c r="C7" s="106"/>
-      <c r="D7" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="106"/>
-      <c r="F7" s="108" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="109"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
-      <c r="M7" s="109"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="110"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="121"/>
+      <c r="F7" s="126" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="124"/>
+      <c r="Q7" s="124"/>
+      <c r="R7" s="125"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="149">
+      <c r="B8" s="120">
         <v>46281</v>
       </c>
-      <c r="C8" s="106"/>
-      <c r="D8" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="106"/>
-      <c r="F8" s="108" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" s="109"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="109"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="109"/>
-      <c r="R8" s="110"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="121"/>
+      <c r="F8" s="126" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="125"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="124"/>
+      <c r="M8" s="124"/>
+      <c r="N8" s="124"/>
+      <c r="O8" s="124"/>
+      <c r="P8" s="124"/>
+      <c r="Q8" s="124"/>
+      <c r="R8" s="125"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="149">
+      <c r="B9" s="120">
         <v>46282</v>
       </c>
-      <c r="C9" s="106"/>
-      <c r="D9" s="105" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="106"/>
-      <c r="F9" s="151" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="152"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="109"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="109"/>
-      <c r="R9" s="110"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="122" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="121"/>
+      <c r="F9" s="127" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="129"/>
+      <c r="K9" s="124"/>
+      <c r="L9" s="124"/>
+      <c r="M9" s="124"/>
+      <c r="N9" s="124"/>
+      <c r="O9" s="124"/>
+      <c r="P9" s="124"/>
+      <c r="Q9" s="124"/>
+      <c r="R9" s="125"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="105"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="109"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="109"/>
-      <c r="O10" s="109"/>
-      <c r="P10" s="109"/>
-      <c r="Q10" s="109"/>
-      <c r="R10" s="110"/>
+      <c r="B10" s="120">
+        <v>46294</v>
+      </c>
+      <c r="C10" s="121"/>
+      <c r="D10" s="122" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="121"/>
+      <c r="F10" s="126" t="s">
+        <v>191</v>
+      </c>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="124" t="s">
+        <v>192</v>
+      </c>
+      <c r="L10" s="124"/>
+      <c r="M10" s="124"/>
+      <c r="N10" s="124"/>
+      <c r="O10" s="124"/>
+      <c r="P10" s="124"/>
+      <c r="Q10" s="124"/>
+      <c r="R10" s="125"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="105"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="109"/>
-      <c r="M11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="O11" s="109"/>
-      <c r="P11" s="109"/>
-      <c r="Q11" s="109"/>
-      <c r="R11" s="110"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="121"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="124"/>
+      <c r="N11" s="124"/>
+      <c r="O11" s="124"/>
+      <c r="P11" s="124"/>
+      <c r="Q11" s="124"/>
+      <c r="R11" s="125"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="109"/>
-      <c r="L12" s="109"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="109"/>
-      <c r="O12" s="109"/>
-      <c r="P12" s="109"/>
-      <c r="Q12" s="109"/>
-      <c r="R12" s="110"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
+      <c r="M12" s="124"/>
+      <c r="N12" s="124"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="124"/>
+      <c r="Q12" s="124"/>
+      <c r="R12" s="125"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="109"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="109"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="110"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="121"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="124"/>
+      <c r="N13" s="124"/>
+      <c r="O13" s="124"/>
+      <c r="P13" s="124"/>
+      <c r="Q13" s="124"/>
+      <c r="R13" s="125"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="107"/>
-      <c r="H14" s="106"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="109"/>
-      <c r="K14" s="109"/>
-      <c r="L14" s="109"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="109"/>
-      <c r="O14" s="109"/>
-      <c r="P14" s="109"/>
-      <c r="Q14" s="109"/>
-      <c r="R14" s="110"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="124"/>
+      <c r="L14" s="124"/>
+      <c r="M14" s="124"/>
+      <c r="N14" s="124"/>
+      <c r="O14" s="124"/>
+      <c r="P14" s="124"/>
+      <c r="Q14" s="124"/>
+      <c r="R14" s="125"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="109"/>
-      <c r="R15" s="110"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="124"/>
+      <c r="L15" s="124"/>
+      <c r="M15" s="124"/>
+      <c r="N15" s="124"/>
+      <c r="O15" s="124"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="124"/>
+      <c r="R15" s="125"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="109"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="109"/>
-      <c r="Q16" s="109"/>
-      <c r="R16" s="110"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
+      <c r="M16" s="124"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="124"/>
+      <c r="P16" s="124"/>
+      <c r="Q16" s="124"/>
+      <c r="R16" s="125"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="106"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="109"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="109"/>
-      <c r="O17" s="109"/>
-      <c r="P17" s="109"/>
-      <c r="Q17" s="109"/>
-      <c r="R17" s="110"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="124"/>
+      <c r="N17" s="124"/>
+      <c r="O17" s="124"/>
+      <c r="P17" s="124"/>
+      <c r="Q17" s="124"/>
+      <c r="R17" s="125"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="105"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="109"/>
-      <c r="O18" s="109"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="110"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="121"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
+      <c r="M18" s="124"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="124"/>
+      <c r="P18" s="124"/>
+      <c r="Q18" s="124"/>
+      <c r="R18" s="125"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="105"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="105"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="109"/>
-      <c r="L19" s="109"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="109"/>
-      <c r="O19" s="109"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="110"/>
+      <c r="B19" s="122"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="124"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="124"/>
+      <c r="P19" s="124"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="125"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="109"/>
-      <c r="O20" s="109"/>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="109"/>
-      <c r="R20" s="110"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="124"/>
+      <c r="O20" s="124"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="124"/>
+      <c r="R20" s="125"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="105"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="110"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="121"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="124"/>
+      <c r="L21" s="124"/>
+      <c r="M21" s="124"/>
+      <c r="N21" s="124"/>
+      <c r="O21" s="124"/>
+      <c r="P21" s="124"/>
+      <c r="Q21" s="124"/>
+      <c r="R21" s="125"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="108"/>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="109"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="109"/>
-      <c r="R22" s="110"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="121"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="121"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="124"/>
+      <c r="L22" s="124"/>
+      <c r="M22" s="124"/>
+      <c r="N22" s="124"/>
+      <c r="O22" s="124"/>
+      <c r="P22" s="124"/>
+      <c r="Q22" s="124"/>
+      <c r="R22" s="125"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -4050,86 +4050,86 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:R6"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:O2"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:R22"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:R4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4138,63 +4138,65 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFF7F1E-AE30-4269-AC6F-F8A3C5E0A4BA}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="16" max="16" width="10" style="159" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" style="84" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="86" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="95" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="158">
+      <c r="P1" s="83">
         <v>46282</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
       <c r="M2" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N2" s="28"/>
       <c r="O2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="158"/>
+        <v>14</v>
+      </c>
+      <c r="P2" s="83">
+        <v>46294</v>
+      </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="31"/>
@@ -4215,28 +4217,28 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="131"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="133"/>
       <c r="H4" s="30"/>
       <c r="I4" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="129" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="131"/>
+      <c r="K4" s="132"/>
+      <c r="L4" s="132"/>
+      <c r="M4" s="132"/>
+      <c r="N4" s="132"/>
+      <c r="O4" s="133"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="16"/>
@@ -4257,10 +4259,10 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4268,10 +4270,10 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="I6" s="35" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K6" s="30"/>
       <c r="L6" s="30"/>
@@ -4280,22 +4282,22 @@
       <c r="O6" s="30"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="156" t="s">
-        <v>162</v>
+      <c r="A7" s="81" t="s">
+        <v>158</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
-      <c r="I7" s="156" t="s">
-        <v>164</v>
+      <c r="I7" s="81" t="s">
+        <v>160</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -4304,22 +4306,22 @@
       <c r="O7" s="30"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="156" t="s">
-        <v>166</v>
+      <c r="A8" s="81" t="s">
+        <v>162</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
-      <c r="I8" s="156" t="s">
-        <v>168</v>
+      <c r="I8" s="81" t="s">
+        <v>164</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -4328,22 +4330,22 @@
       <c r="O8" s="34"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="156" t="s">
-        <v>170</v>
+      <c r="A9" s="81" t="s">
+        <v>166</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
-      <c r="I9" s="156" t="s">
-        <v>168</v>
+      <c r="I9" s="81" t="s">
+        <v>164</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -4352,11 +4354,11 @@
       <c r="O9" s="30"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="156" t="s">
-        <v>172</v>
+      <c r="A10" s="81" t="s">
+        <v>168</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4373,7 +4375,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4381,7 +4383,7 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="I11" s="35" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -4398,11 +4400,11 @@
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
-      <c r="I12" s="157" t="s">
-        <v>176</v>
+      <c r="I12" s="82" t="s">
+        <v>172</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -4412,10 +4414,10 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="35" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4424,7 +4426,7 @@
       <c r="G13" s="30"/>
       <c r="I13" s="35"/>
       <c r="J13" s="30" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -4433,11 +4435,11 @@
       <c r="O13" s="30"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="157" t="s">
-        <v>180</v>
+      <c r="A14" s="82" t="s">
+        <v>176</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4445,7 +4447,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="J14" s="30" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -4454,7 +4456,7 @@
       <c r="O14" s="30"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="157"/>
+      <c r="A15" s="82"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
@@ -4470,10 +4472,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4482,7 +4484,7 @@
       <c r="G16" s="30"/>
       <c r="H16" s="7"/>
       <c r="I16" s="16" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -4492,11 +4494,11 @@
       <c r="O16" s="30"/>
     </row>
     <row r="17" spans="1:15" ht="26.5">
-      <c r="A17" s="157" t="s">
-        <v>185</v>
+      <c r="A17" s="82" t="s">
+        <v>181</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4504,11 +4506,11 @@
       <c r="F17" s="30"/>
       <c r="G17" s="30"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="157" t="s">
-        <v>182</v>
+      <c r="I17" s="82" t="s">
+        <v>178</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
@@ -4517,11 +4519,11 @@
       <c r="O17" s="30"/>
     </row>
     <row r="18" spans="1:15" ht="26.5">
-      <c r="A18" s="157" t="s">
-        <v>187</v>
+      <c r="A18" s="82" t="s">
+        <v>183</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -4555,17 +4557,13 @@
       <c r="O19" s="36"/>
     </row>
     <row r="20" spans="1:15" ht="26.5">
-      <c r="A20" s="35">
-        <v>3.2</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="36"/>
@@ -4576,19 +4574,15 @@
       <c r="O20" s="36"/>
     </row>
     <row r="21" spans="1:15" ht="26.5">
-      <c r="A21" s="35">
-        <v>3.3</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
       <c r="J21" s="36"/>
       <c r="K21" s="36"/>
       <c r="L21" s="36"/>
@@ -4596,8 +4590,8 @@
       <c r="N21" s="36"/>
       <c r="O21" s="36"/>
     </row>
-    <row r="22" spans="1:15" ht="26.5">
-      <c r="A22" s="36"/>
+    <row r="22" spans="1:15">
+      <c r="A22" s="7"/>
       <c r="B22" s="16"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -4606,46 +4600,12 @@
       <c r="G22" s="16"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-    </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="7"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4668,54 +4628,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="139"/>
       <c r="L2" s="29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="26"/>
       <c r="N2" s="29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="72"/>
     </row>
@@ -4739,7 +4699,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4757,27 +4717,27 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="133" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
+      <c r="B5" s="140" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="34"/>
       <c r="B6" s="34" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -4813,7 +4773,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -4829,40 +4789,42 @@
       <c r="N8" s="8"/>
       <c r="O8" s="34"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="18" customHeight="1">
       <c r="A9" s="34"/>
-      <c r="B9" s="134" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="134"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="134"/>
-      <c r="N9" s="134"/>
+      <c r="B9" s="141" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="141"/>
       <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
+      <c r="B10" s="141" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="141"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="141"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="141"/>
+      <c r="N10" s="141"/>
       <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:15">
@@ -4885,7 +4847,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="34" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -4903,115 +4865,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="34"/>
-      <c r="B13" s="132" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="132"/>
-      <c r="N13" s="132"/>
-      <c r="O13" s="132"/>
+      <c r="B13" s="134" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="134"/>
+      <c r="O13" s="134"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="34"/>
-      <c r="B14" s="132" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="132"/>
-      <c r="O14" s="132"/>
+      <c r="B14" s="134" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="134"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="134"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="134"/>
+      <c r="O14" s="134"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="34"/>
-      <c r="B15" s="132" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-      <c r="M15" s="132"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="132"/>
+      <c r="B15" s="134" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="134"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="134"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="134"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="34"/>
-      <c r="B16" s="132" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="132"/>
-      <c r="K16" s="132"/>
-      <c r="L16" s="132"/>
-      <c r="M16" s="132"/>
-      <c r="N16" s="132"/>
-      <c r="O16" s="132"/>
+      <c r="B16" s="134" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="134"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="134"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="134"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="34"/>
-      <c r="B17" s="132" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="132"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="132"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
+      <c r="B17" s="134" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="134"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="132"/>
-      <c r="K18" s="132"/>
-      <c r="L18" s="132"/>
-      <c r="M18" s="132"/>
-      <c r="N18" s="132"/>
-      <c r="O18" s="132"/>
+      <c r="B18" s="134"/>
+      <c r="C18" s="134"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="134"/>
+      <c r="N18" s="134"/>
+      <c r="O18" s="134"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
@@ -5033,7 +4995,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="41" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -5052,7 +5014,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
       <c r="B21" s="41" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
@@ -5105,7 +5067,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -5124,7 +5086,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="44" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="45"/>
@@ -5143,7 +5105,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="44" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -5162,7 +5124,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -5197,7 +5159,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -5216,7 +5178,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="46" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -5235,7 +5197,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="46" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -5254,7 +5216,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5288,7 +5250,7 @@
       <c r="O33" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B18:O18"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
@@ -5301,7 +5263,8 @@
     <mergeCell ref="B15:O15"/>
     <mergeCell ref="B16:O16"/>
     <mergeCell ref="B17:O17"/>
-    <mergeCell ref="B9:N10"/>
+    <mergeCell ref="B9:N9"/>
+    <mergeCell ref="B10:N10"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5317,28 +5280,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="135" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -5348,23 +5311,23 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="139"/>
       <c r="L2" s="29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="26"/>
       <c r="N2" s="29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="72"/>
     </row>
@@ -5388,7 +5351,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5423,12 +5386,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="34"/>
-      <c r="B6" s="137" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="138"/>
+      <c r="B6" s="144" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="145"/>
       <c r="D6" s="74" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="49"/>
@@ -5444,12 +5407,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
-      <c r="B7" s="135" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="136"/>
+      <c r="B7" s="142" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="143"/>
       <c r="D7" s="17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -5465,12 +5428,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
-      <c r="B8" s="135" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="136"/>
+      <c r="B8" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="143"/>
       <c r="D8" s="17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5934,16 +5897,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="91"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="136"/>
       <c r="E1" s="70" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F1" s="70"/>
       <c r="G1" s="70"/>
@@ -5954,36 +5917,36 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="139" t="s">
-        <v>116</v>
-      </c>
-      <c r="O1" s="139"/>
+      <c r="N1" s="149" t="s">
+        <v>112</v>
+      </c>
+      <c r="O1" s="149"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="139"/>
       <c r="K2" s="29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L2" s="28"/>
       <c r="M2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="140"/>
-      <c r="O2" s="140"/>
+        <v>14</v>
+      </c>
+      <c r="N2" s="150"/>
+      <c r="O2" s="150"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="39"/>
@@ -6005,7 +5968,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6041,12 +6004,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="34"/>
       <c r="B6" s="48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F6" s="49"/>
       <c r="G6" s="49"/>
@@ -6054,7 +6017,7 @@
       <c r="I6" s="50"/>
       <c r="J6" s="65"/>
       <c r="K6" s="48" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L6" s="54"/>
       <c r="M6" s="69"/>
@@ -6064,12 +6027,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
       <c r="E7" s="67" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="53"/>
@@ -6077,7 +6040,7 @@
       <c r="I7" s="53"/>
       <c r="J7" s="54"/>
       <c r="K7" s="68" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L7" s="54"/>
       <c r="M7" s="30"/>
@@ -6087,12 +6050,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
       <c r="E8" s="67" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="53"/>
@@ -6100,7 +6063,7 @@
       <c r="I8" s="53"/>
       <c r="J8" s="54"/>
       <c r="K8" s="68" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L8" s="54"/>
       <c r="M8" s="30"/>
@@ -6110,12 +6073,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="53"/>
       <c r="E9" s="67" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="53"/>
@@ -6123,7 +6086,7 @@
       <c r="I9" s="53"/>
       <c r="J9" s="54"/>
       <c r="K9" s="68" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L9" s="54"/>
       <c r="M9" s="30"/>
@@ -6133,20 +6096,20 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="17" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="80" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="82"/>
+      <c r="E10" s="146" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
+      <c r="H10" s="147"/>
+      <c r="I10" s="147"/>
+      <c r="J10" s="148"/>
       <c r="K10" s="68" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L10" s="54"/>
       <c r="M10" s="30"/>
@@ -6155,13 +6118,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
-      <c r="B11" s="80" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="82"/>
+      <c r="B11" s="146" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="147"/>
+      <c r="D11" s="148"/>
       <c r="E11" s="67" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="53"/>
@@ -6169,7 +6132,7 @@
       <c r="I11" s="53"/>
       <c r="J11" s="54"/>
       <c r="K11" s="68" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L11" s="54"/>
       <c r="M11" s="30"/>
@@ -6196,7 +6159,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
       <c r="B13" s="34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
@@ -6204,7 +6167,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
       <c r="B14" s="41" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="41"/>
@@ -6223,7 +6186,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
       <c r="B15" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
@@ -6231,7 +6194,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="56"/>
       <c r="H15" s="56" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I15" s="56"/>
       <c r="J15" s="41"/>
@@ -6244,7 +6207,7 @@
     <row r="16" spans="1:15">
       <c r="A16" s="34"/>
       <c r="B16" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
@@ -6280,7 +6243,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
@@ -6299,7 +6262,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="56" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -6318,7 +6281,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
@@ -6354,7 +6317,7 @@
     <row r="22" spans="1:15">
       <c r="A22" s="34"/>
       <c r="B22" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
@@ -6373,7 +6336,7 @@
     <row r="23" spans="1:15" ht="18" customHeight="1">
       <c r="A23" s="43"/>
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C23" s="43"/>
       <c r="D23" s="43"/>
@@ -6392,7 +6355,7 @@
     <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="56" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -6427,7 +6390,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="41" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -6446,7 +6409,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="56" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -6465,7 +6428,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="56" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -6484,7 +6447,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="56" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -6503,7 +6466,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="56" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="45"/>
@@ -6539,7 +6502,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="56" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
@@ -6558,7 +6521,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6667,28 +6630,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6698,23 +6661,23 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="139"/>
       <c r="L2" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="57"/>
       <c r="N2" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="26"/>
     </row>
@@ -6738,7 +6701,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6757,7 +6720,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="30" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -6793,7 +6756,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
@@ -6812,7 +6775,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -6848,7 +6811,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -6867,7 +6830,7 @@
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
       <c r="B11" s="41" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="41"/>
@@ -7211,28 +7174,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="135" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7242,23 +7205,23 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="139"/>
       <c r="L2" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="57"/>
       <c r="N2" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="26"/>
     </row>
@@ -7282,7 +7245,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7301,23 +7264,23 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="59" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="59" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" s="60"/>
       <c r="F5" s="59" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="60"/>
       <c r="H5" s="59" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I5" s="60"/>
       <c r="J5" s="59" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K5" s="53"/>
       <c r="L5" s="61"/>
@@ -7328,11 +7291,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="52" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="52" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E6" s="55"/>
       <c r="F6" s="52">
@@ -7340,11 +7303,11 @@
       </c>
       <c r="G6" s="55"/>
       <c r="H6" s="52" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I6" s="55"/>
       <c r="J6" s="52" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K6" s="53"/>
       <c r="L6" s="61"/>
@@ -7355,11 +7318,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="52" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="52">
@@ -7367,11 +7330,11 @@
       </c>
       <c r="G7" s="55"/>
       <c r="H7" s="52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I7" s="55"/>
       <c r="J7" s="52" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K7" s="53"/>
       <c r="L7" s="61"/>
@@ -7382,11 +7345,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="52">
@@ -7394,11 +7357,11 @@
       </c>
       <c r="G8" s="55"/>
       <c r="H8" s="52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I8" s="55"/>
       <c r="J8" s="52" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="53"/>
@@ -7409,11 +7372,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="52" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="52">
@@ -7421,26 +7384,26 @@
       </c>
       <c r="G9" s="55"/>
       <c r="H9" s="52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I9" s="55"/>
-      <c r="J9" s="83" t="s">
-        <v>135</v>
-      </c>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="85"/>
+      <c r="J9" s="154" t="s">
+        <v>131</v>
+      </c>
+      <c r="K9" s="155"/>
+      <c r="L9" s="155"/>
+      <c r="M9" s="156"/>
       <c r="N9" s="34"/>
       <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C10" s="55"/>
       <c r="D10" s="52" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E10" s="55"/>
       <c r="F10" s="52">
@@ -7448,11 +7411,11 @@
       </c>
       <c r="G10" s="55"/>
       <c r="H10" s="52" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="75" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="53"/>
@@ -7463,11 +7426,11 @@
     <row r="11" spans="1:15" ht="54" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="67" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C11" s="55"/>
       <c r="D11" s="52" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E11" s="55"/>
       <c r="F11" s="17">
@@ -7475,38 +7438,38 @@
       </c>
       <c r="G11" s="55"/>
       <c r="H11" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I11" s="23"/>
-      <c r="J11" s="77" t="s">
-        <v>140</v>
-      </c>
-      <c r="K11" s="78"/>
-      <c r="L11" s="78"/>
-      <c r="M11" s="79"/>
+      <c r="J11" s="151" t="s">
+        <v>136</v>
+      </c>
+      <c r="K11" s="152"/>
+      <c r="L11" s="152"/>
+      <c r="M11" s="153"/>
       <c r="N11" s="8"/>
       <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E12" s="55"/>
       <c r="F12" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I12" s="55"/>
       <c r="J12" s="17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7517,23 +7480,23 @@
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
       <c r="B13" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I13" s="55"/>
       <c r="J13" s="17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -7544,11 +7507,11 @@
     <row r="14" spans="1:15" ht="36" customHeight="1">
       <c r="A14" s="34"/>
       <c r="B14" s="52" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C14" s="73"/>
       <c r="D14" s="52" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E14" s="55"/>
       <c r="F14" s="17">
@@ -7556,15 +7519,15 @@
       </c>
       <c r="G14" s="55"/>
       <c r="H14" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I14" s="55"/>
-      <c r="J14" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="82"/>
+      <c r="J14" s="146" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="147"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="148"/>
       <c r="N14" s="41"/>
       <c r="O14" s="41"/>
     </row>
@@ -7605,7 +7568,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="41" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -7624,23 +7587,23 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="59" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="59" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E18" s="60"/>
       <c r="F18" s="59" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" s="60"/>
       <c r="H18" s="59" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I18" s="60"/>
       <c r="J18" s="59" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K18" s="53"/>
       <c r="L18" s="61"/>
@@ -7651,11 +7614,11 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="52" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="52" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" s="55"/>
       <c r="F19" s="52">
@@ -7663,11 +7626,11 @@
       </c>
       <c r="G19" s="55"/>
       <c r="H19" s="52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I19" s="55"/>
       <c r="J19" s="52" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K19" s="53"/>
       <c r="L19" s="61"/>
@@ -7678,11 +7641,11 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="52" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E20" s="55"/>
       <c r="F20" s="52">
@@ -7690,11 +7653,11 @@
       </c>
       <c r="G20" s="55"/>
       <c r="H20" s="52" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I20" s="55"/>
       <c r="J20" s="52" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="53"/>
@@ -7705,11 +7668,11 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="52" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C21" s="55"/>
       <c r="D21" s="52" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="52">
@@ -7717,11 +7680,11 @@
       </c>
       <c r="G21" s="55"/>
       <c r="H21" s="52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I21" s="55"/>
       <c r="J21" s="52" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="53"/>
@@ -7732,11 +7695,11 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C22" s="55"/>
       <c r="D22" s="52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="52">
@@ -7744,7 +7707,7 @@
       </c>
       <c r="G22" s="55"/>
       <c r="H22" s="52" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="75"/>
@@ -7757,11 +7720,11 @@
     <row r="23" spans="1:15" ht="36" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="67" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="52" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E23" s="55"/>
       <c r="F23" s="17">
@@ -7769,38 +7732,38 @@
       </c>
       <c r="G23" s="55"/>
       <c r="H23" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I23" s="23"/>
-      <c r="J23" s="77" t="s">
-        <v>143</v>
-      </c>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="79"/>
+      <c r="J23" s="151" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="152"/>
+      <c r="L23" s="152"/>
+      <c r="M23" s="153"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E24" s="55"/>
       <c r="F24" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G24" s="55"/>
       <c r="H24" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I24" s="55"/>
       <c r="J24" s="17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -7811,23 +7774,23 @@
     <row r="25" spans="1:15" ht="18" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C25" s="54"/>
       <c r="D25" s="52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G25" s="55"/>
       <c r="H25" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I25" s="55"/>
       <c r="J25" s="17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
@@ -7838,11 +7801,11 @@
     <row r="26" spans="1:15" ht="36" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="52" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C26" s="73"/>
       <c r="D26" s="52" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E26" s="55"/>
       <c r="F26" s="17">
@@ -7850,15 +7813,15 @@
       </c>
       <c r="G26" s="55"/>
       <c r="H26" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I26" s="55"/>
-      <c r="J26" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="K26" s="81"/>
-      <c r="L26" s="81"/>
-      <c r="M26" s="82"/>
+      <c r="J26" s="146" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="147"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="148"/>
       <c r="N26" s="56"/>
       <c r="O26" s="56"/>
     </row>
@@ -8023,28 +7986,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="91"/>
-      <c r="E1" s="92" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="135" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="136"/>
+      <c r="E1" s="137" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="139"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -8054,23 +8017,23 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="94"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="139"/>
       <c r="L2" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="57"/>
       <c r="N2" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="26"/>
     </row>
@@ -8114,21 +8077,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="50"/>
       <c r="E5" s="64"/>
       <c r="F5" s="50"/>
       <c r="G5" s="60"/>
       <c r="H5" s="59" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I5" s="64"/>
       <c r="J5" s="50"/>
       <c r="K5" s="50"/>
       <c r="L5" s="65"/>
       <c r="M5" s="59" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N5" s="61"/>
       <c r="O5" s="55"/>
@@ -8139,25 +8102,25 @@
         <v>1</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" s="141"/>
-      <c r="E6" s="142"/>
-      <c r="F6" s="141"/>
+        <v>145</v>
+      </c>
+      <c r="D6" s="77"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="77"/>
       <c r="G6" s="76"/>
       <c r="H6" s="75" t="s">
-        <v>150</v>
-      </c>
-      <c r="I6" s="142"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="141"/>
-      <c r="L6" s="143"/>
-      <c r="M6" s="77" t="s">
-        <v>151</v>
-      </c>
-      <c r="N6" s="78"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="144"/>
+        <v>146</v>
+      </c>
+      <c r="I6" s="78"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="151" t="s">
+        <v>147</v>
+      </c>
+      <c r="N6" s="152"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="80"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="34"/>
@@ -8165,43 +8128,43 @@
         <v>2</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="141"/>
-      <c r="E7" s="142"/>
-      <c r="F7" s="141"/>
+        <v>148</v>
+      </c>
+      <c r="D7" s="77"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="77"/>
       <c r="G7" s="76"/>
       <c r="H7" s="75" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" s="142"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="143"/>
-      <c r="M7" s="145" t="s">
-        <v>154</v>
-      </c>
-      <c r="N7" s="146"/>
-      <c r="O7" s="147"/>
-      <c r="P7" s="144"/>
+        <v>149</v>
+      </c>
+      <c r="I7" s="78"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="157" t="s">
+        <v>150</v>
+      </c>
+      <c r="N7" s="158"/>
+      <c r="O7" s="159"/>
+      <c r="P7" s="80"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="34"/>
       <c r="B8" s="66"/>
       <c r="C8" s="75"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="142"/>
-      <c r="F8" s="142"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
       <c r="G8" s="76"/>
       <c r="H8" s="75"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="143"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="79"/>
       <c r="M8" s="75"/>
-      <c r="N8" s="142"/>
+      <c r="N8" s="78"/>
       <c r="O8" s="76"/>
-      <c r="P8" s="144"/>
+      <c r="P8" s="80"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="34"/>
